--- a/load-report.xlsx
+++ b/load-report.xlsx
@@ -59,7 +59,7 @@
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>4.37s</t>
+    <t>4.30s</t>
   </si>
   <si>
     <t>Fast Execution</t>
@@ -68,7 +68,7 @@
     <t>Average Case Speed</t>
   </si>
   <si>
-    <t>14.6ms</t>
+    <t>14.3ms</t>
   </si>
   <si>
     <t>Optimal Pacing</t>
@@ -104,7 +104,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-26 03:33:53</t>
+    <t>2026-08-27 02:59:33</t>
   </si>
   <si>
     <t>PERF_LOD_002</t>
@@ -113,7 +113,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:03</t>
+    <t>2026-08-27 02:59:43</t>
   </si>
   <si>
     <t>PERF_LOD_003</t>
@@ -122,7 +122,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:13</t>
+    <t>2026-08-27 02:59:53</t>
   </si>
   <si>
     <t>PERF_LOD_004</t>
@@ -131,7 +131,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:23</t>
+    <t>2026-08-27 03:00:03</t>
   </si>
   <si>
     <t>PERF_LOD_005</t>
@@ -140,7 +140,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:33</t>
+    <t>2026-08-27 03:00:13</t>
   </si>
   <si>
     <t>PERF_LOD_006</t>
@@ -149,7 +149,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:43</t>
+    <t>2026-08-27 03:00:23</t>
   </si>
   <si>
     <t>PERF_LOD_007</t>
@@ -158,7 +158,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:34:53</t>
+    <t>2026-08-27 03:00:33</t>
   </si>
   <si>
     <t>PERF_LOD_008</t>
@@ -167,7 +167,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:03</t>
+    <t>2026-08-27 03:00:43</t>
   </si>
   <si>
     <t>PERF_LOD_009</t>
@@ -176,7 +176,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:13</t>
+    <t>2026-08-27 03:00:53</t>
   </si>
   <si>
     <t>PERF_LOD_010</t>
@@ -185,7 +185,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:23</t>
+    <t>2026-08-27 03:01:03</t>
   </si>
   <si>
     <t>PERF_LOD_011</t>
@@ -194,7 +194,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:33</t>
+    <t>2026-08-27 03:01:13</t>
   </si>
   <si>
     <t>PERF_LOD_012</t>
@@ -203,7 +203,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:43</t>
+    <t>2026-08-27 03:01:23</t>
   </si>
   <si>
     <t>PERF_LOD_013</t>
@@ -212,7 +212,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 03:35:53</t>
+    <t>2026-08-27 03:01:33</t>
   </si>
   <si>
     <t>PERF_LOD_014</t>
@@ -221,7 +221,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:03</t>
+    <t>2026-08-27 03:01:43</t>
   </si>
   <si>
     <t>PERF_LOD_015</t>
@@ -230,7 +230,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:13</t>
+    <t>2026-08-27 03:01:53</t>
   </si>
   <si>
     <t>PERF_LOD_016</t>
@@ -239,7 +239,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:23</t>
+    <t>2026-08-27 03:02:03</t>
   </si>
   <si>
     <t>PERF_LOD_017</t>
@@ -248,7 +248,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:33</t>
+    <t>2026-08-27 03:02:13</t>
   </si>
   <si>
     <t>PERF_LOD_018</t>
@@ -257,7 +257,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:43</t>
+    <t>2026-08-27 03:02:23</t>
   </si>
   <si>
     <t>PERF_LOD_019</t>
@@ -266,7 +266,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 03:36:53</t>
+    <t>2026-08-27 03:02:33</t>
   </si>
   <si>
     <t>PERF_LOD_020</t>
@@ -275,7 +275,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:03</t>
+    <t>2026-08-27 03:02:43</t>
   </si>
   <si>
     <t>PERF_LOD_021</t>
@@ -284,7 +284,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:13</t>
+    <t>2026-08-27 03:02:53</t>
   </si>
   <si>
     <t>PERF_LOD_022</t>
@@ -293,7 +293,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:23</t>
+    <t>2026-08-27 03:03:03</t>
   </si>
   <si>
     <t>PERF_LOD_023</t>
@@ -302,7 +302,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:33</t>
+    <t>2026-08-27 03:03:13</t>
   </si>
   <si>
     <t>PERF_LOD_024</t>
@@ -311,7 +311,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:43</t>
+    <t>2026-08-27 03:03:23</t>
   </si>
   <si>
     <t>PERF_LOD_025</t>
@@ -320,7 +320,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 03:37:53</t>
+    <t>2026-08-27 03:03:33</t>
   </si>
   <si>
     <t>PERF_LOD_026</t>
@@ -329,7 +329,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:03</t>
+    <t>2026-08-27 03:03:43</t>
   </si>
   <si>
     <t>PERF_LOD_027</t>
@@ -338,7 +338,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:13</t>
+    <t>2026-08-27 03:03:53</t>
   </si>
   <si>
     <t>PERF_LOD_028</t>
@@ -347,7 +347,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:23</t>
+    <t>2026-08-27 03:04:03</t>
   </si>
   <si>
     <t>PERF_LOD_029</t>
@@ -356,7 +356,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:33</t>
+    <t>2026-08-27 03:04:13</t>
   </si>
   <si>
     <t>PERF_LOD_030</t>
@@ -365,7 +365,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:43</t>
+    <t>2026-08-27 03:04:23</t>
   </si>
   <si>
     <t>PERF_LOD_031</t>
@@ -377,7 +377,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 03:38:53</t>
+    <t>2026-08-27 03:04:33</t>
   </si>
   <si>
     <t>PERF_LOD_032</t>
@@ -386,7 +386,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:03</t>
+    <t>2026-08-27 03:04:43</t>
   </si>
   <si>
     <t>PERF_LOD_033</t>
@@ -395,7 +395,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:13</t>
+    <t>2026-08-27 03:04:53</t>
   </si>
   <si>
     <t>PERF_LOD_034</t>
@@ -404,7 +404,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:23</t>
+    <t>2026-08-27 03:05:03</t>
   </si>
   <si>
     <t>PERF_LOD_035</t>
@@ -413,7 +413,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:33</t>
+    <t>2026-08-27 03:05:13</t>
   </si>
   <si>
     <t>PERF_LOD_036</t>
@@ -422,7 +422,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:43</t>
+    <t>2026-08-27 03:05:23</t>
   </si>
   <si>
     <t>PERF_LOD_037</t>
@@ -431,7 +431,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:39:53</t>
+    <t>2026-08-27 03:05:33</t>
   </si>
   <si>
     <t>PERF_LOD_038</t>
@@ -440,7 +440,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:03</t>
+    <t>2026-08-27 03:05:43</t>
   </si>
   <si>
     <t>PERF_LOD_039</t>
@@ -449,7 +449,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:13</t>
+    <t>2026-08-27 03:05:53</t>
   </si>
   <si>
     <t>PERF_LOD_040</t>
@@ -458,7 +458,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:23</t>
+    <t>2026-08-27 03:06:03</t>
   </si>
   <si>
     <t>PERF_LOD_041</t>
@@ -467,7 +467,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:33</t>
+    <t>2026-08-27 03:06:13</t>
   </si>
   <si>
     <t>PERF_LOD_042</t>
@@ -476,7 +476,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:43</t>
+    <t>2026-08-27 03:06:23</t>
   </si>
   <si>
     <t>PERF_LOD_043</t>
@@ -485,7 +485,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 03:40:53</t>
+    <t>2026-08-27 03:06:33</t>
   </si>
   <si>
     <t>PERF_LOD_044</t>
@@ -494,7 +494,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:03</t>
+    <t>2026-08-27 03:06:43</t>
   </si>
   <si>
     <t>PERF_LOD_045</t>
@@ -503,7 +503,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:13</t>
+    <t>2026-08-27 03:06:53</t>
   </si>
   <si>
     <t>PERF_LOD_046</t>
@@ -512,7 +512,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:23</t>
+    <t>2026-08-27 03:07:03</t>
   </si>
   <si>
     <t>PERF_LOD_047</t>
@@ -521,7 +521,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:33</t>
+    <t>2026-08-27 03:07:13</t>
   </si>
   <si>
     <t>PERF_LOD_048</t>
@@ -530,7 +530,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:43</t>
+    <t>2026-08-27 03:07:23</t>
   </si>
   <si>
     <t>PERF_LOD_049</t>
@@ -539,7 +539,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 03:41:53</t>
+    <t>2026-08-27 03:07:33</t>
   </si>
   <si>
     <t>PERF_LOD_050</t>
@@ -548,7 +548,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:03</t>
+    <t>2026-08-27 03:07:43</t>
   </si>
   <si>
     <t>PERF_LOD_051</t>
@@ -557,7 +557,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:13</t>
+    <t>2026-08-27 03:07:53</t>
   </si>
   <si>
     <t>PERF_LOD_052</t>
@@ -566,7 +566,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:23</t>
+    <t>2026-08-27 03:08:03</t>
   </si>
   <si>
     <t>PERF_LOD_053</t>
@@ -575,7 +575,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:33</t>
+    <t>2026-08-27 03:08:13</t>
   </si>
   <si>
     <t>PERF_LOD_054</t>
@@ -584,7 +584,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:43</t>
+    <t>2026-08-27 03:08:23</t>
   </si>
   <si>
     <t>PERF_LOD_055</t>
@@ -593,7 +593,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 03:42:53</t>
+    <t>2026-08-27 03:08:33</t>
   </si>
   <si>
     <t>PERF_LOD_056</t>
@@ -602,7 +602,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:03</t>
+    <t>2026-08-27 03:08:43</t>
   </si>
   <si>
     <t>PERF_LOD_057</t>
@@ -611,7 +611,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:13</t>
+    <t>2026-08-27 03:08:53</t>
   </si>
   <si>
     <t>PERF_LOD_058</t>
@@ -620,7 +620,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:23</t>
+    <t>2026-08-27 03:09:03</t>
   </si>
   <si>
     <t>PERF_LOD_059</t>
@@ -629,7 +629,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:33</t>
+    <t>2026-08-27 03:09:13</t>
   </si>
   <si>
     <t>PERF_LOD_060</t>
@@ -638,7 +638,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:43</t>
+    <t>2026-08-27 03:09:23</t>
   </si>
   <si>
     <t>PERF_LOD_061</t>
@@ -650,7 +650,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 03:43:53</t>
+    <t>2026-08-27 03:09:33</t>
   </si>
   <si>
     <t>PERF_LOD_062</t>
@@ -659,7 +659,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:03</t>
+    <t>2026-08-27 03:09:43</t>
   </si>
   <si>
     <t>PERF_LOD_063</t>
@@ -668,7 +668,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:13</t>
+    <t>2026-08-27 03:09:53</t>
   </si>
   <si>
     <t>PERF_LOD_064</t>
@@ -677,7 +677,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:23</t>
+    <t>2026-08-27 03:10:03</t>
   </si>
   <si>
     <t>PERF_LOD_065</t>
@@ -686,7 +686,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:33</t>
+    <t>2026-08-27 03:10:13</t>
   </si>
   <si>
     <t>PERF_LOD_066</t>
@@ -695,7 +695,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:43</t>
+    <t>2026-08-27 03:10:23</t>
   </si>
   <si>
     <t>PERF_LOD_067</t>
@@ -704,7 +704,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:44:53</t>
+    <t>2026-08-27 03:10:33</t>
   </si>
   <si>
     <t>PERF_LOD_068</t>
@@ -713,7 +713,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:03</t>
+    <t>2026-08-27 03:10:43</t>
   </si>
   <si>
     <t>PERF_LOD_069</t>
@@ -722,7 +722,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:13</t>
+    <t>2026-08-27 03:10:53</t>
   </si>
   <si>
     <t>PERF_LOD_070</t>
@@ -731,7 +731,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:23</t>
+    <t>2026-08-27 03:11:03</t>
   </si>
   <si>
     <t>PERF_LOD_071</t>
@@ -740,7 +740,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:33</t>
+    <t>2026-08-27 03:11:13</t>
   </si>
   <si>
     <t>PERF_LOD_072</t>
@@ -749,7 +749,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:43</t>
+    <t>2026-08-27 03:11:23</t>
   </si>
   <si>
     <t>PERF_LOD_073</t>
@@ -758,7 +758,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 03:45:53</t>
+    <t>2026-08-27 03:11:33</t>
   </si>
   <si>
     <t>PERF_LOD_074</t>
@@ -767,7 +767,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:03</t>
+    <t>2026-08-27 03:11:43</t>
   </si>
   <si>
     <t>PERF_LOD_075</t>
@@ -776,7 +776,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:13</t>
+    <t>2026-08-27 03:11:53</t>
   </si>
   <si>
     <t>PERF_LOD_076</t>
@@ -785,7 +785,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:23</t>
+    <t>2026-08-27 03:12:03</t>
   </si>
   <si>
     <t>PERF_LOD_077</t>
@@ -794,7 +794,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:33</t>
+    <t>2026-08-27 03:12:13</t>
   </si>
   <si>
     <t>PERF_LOD_078</t>
@@ -803,7 +803,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:43</t>
+    <t>2026-08-27 03:12:23</t>
   </si>
   <si>
     <t>PERF_LOD_079</t>
@@ -812,7 +812,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 03:46:53</t>
+    <t>2026-08-27 03:12:33</t>
   </si>
   <si>
     <t>PERF_LOD_080</t>
@@ -821,7 +821,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:03</t>
+    <t>2026-08-27 03:12:43</t>
   </si>
   <si>
     <t>PERF_LOD_081</t>
@@ -830,7 +830,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:13</t>
+    <t>2026-08-27 03:12:53</t>
   </si>
   <si>
     <t>PERF_LOD_082</t>
@@ -839,7 +839,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:23</t>
+    <t>2026-08-27 03:13:03</t>
   </si>
   <si>
     <t>PERF_LOD_083</t>
@@ -848,7 +848,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:33</t>
+    <t>2026-08-27 03:13:13</t>
   </si>
   <si>
     <t>PERF_LOD_084</t>
@@ -857,7 +857,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:43</t>
+    <t>2026-08-27 03:13:23</t>
   </si>
   <si>
     <t>PERF_LOD_085</t>
@@ -866,7 +866,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 03:47:53</t>
+    <t>2026-08-27 03:13:33</t>
   </si>
   <si>
     <t>PERF_LOD_086</t>
@@ -875,7 +875,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:03</t>
+    <t>2026-08-27 03:13:43</t>
   </si>
   <si>
     <t>PERF_LOD_087</t>
@@ -884,7 +884,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:13</t>
+    <t>2026-08-27 03:13:53</t>
   </si>
   <si>
     <t>PERF_LOD_088</t>
@@ -893,7 +893,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:23</t>
+    <t>2026-08-27 03:14:03</t>
   </si>
   <si>
     <t>PERF_LOD_089</t>
@@ -902,7 +902,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:33</t>
+    <t>2026-08-27 03:14:13</t>
   </si>
   <si>
     <t>PERF_LOD_090</t>
@@ -911,7 +911,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:43</t>
+    <t>2026-08-27 03:14:23</t>
   </si>
   <si>
     <t>PERF_LOD_091</t>
@@ -923,7 +923,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 03:48:53</t>
+    <t>2026-08-27 03:14:33</t>
   </si>
   <si>
     <t>PERF_LOD_092</t>
@@ -932,7 +932,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:03</t>
+    <t>2026-08-27 03:14:43</t>
   </si>
   <si>
     <t>PERF_LOD_093</t>
@@ -941,7 +941,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:13</t>
+    <t>2026-08-27 03:14:53</t>
   </si>
   <si>
     <t>PERF_LOD_094</t>
@@ -950,7 +950,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:23</t>
+    <t>2026-08-27 03:15:03</t>
   </si>
   <si>
     <t>PERF_LOD_095</t>
@@ -959,7 +959,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:33</t>
+    <t>2026-08-27 03:15:13</t>
   </si>
   <si>
     <t>PERF_LOD_096</t>
@@ -968,7 +968,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:43</t>
+    <t>2026-08-27 03:15:23</t>
   </si>
   <si>
     <t>PERF_LOD_097</t>
@@ -977,7 +977,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:49:53</t>
+    <t>2026-08-27 03:15:33</t>
   </si>
   <si>
     <t>PERF_LOD_098</t>
@@ -986,7 +986,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:03</t>
+    <t>2026-08-27 03:15:43</t>
   </si>
   <si>
     <t>PERF_LOD_099</t>
@@ -995,7 +995,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:13</t>
+    <t>2026-08-27 03:15:53</t>
   </si>
   <si>
     <t>PERF_LOD_100</t>
@@ -1004,7 +1004,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:23</t>
+    <t>2026-08-27 03:16:03</t>
   </si>
   <si>
     <t>PERF_LOD_101</t>
@@ -1013,7 +1013,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:33</t>
+    <t>2026-08-27 03:16:13</t>
   </si>
   <si>
     <t>PERF_LOD_102</t>
@@ -1022,7 +1022,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:43</t>
+    <t>2026-08-27 03:16:23</t>
   </si>
   <si>
     <t>PERF_LOD_103</t>
@@ -1031,7 +1031,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 03:50:53</t>
+    <t>2026-08-27 03:16:33</t>
   </si>
   <si>
     <t>PERF_LOD_104</t>
@@ -1040,7 +1040,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:03</t>
+    <t>2026-08-27 03:16:43</t>
   </si>
   <si>
     <t>PERF_LOD_105</t>
@@ -1049,7 +1049,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:13</t>
+    <t>2026-08-27 03:16:53</t>
   </si>
   <si>
     <t>PERF_LOD_106</t>
@@ -1058,7 +1058,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:23</t>
+    <t>2026-08-27 03:17:03</t>
   </si>
   <si>
     <t>PERF_LOD_107</t>
@@ -1067,7 +1067,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:33</t>
+    <t>2026-08-27 03:17:13</t>
   </si>
   <si>
     <t>PERF_LOD_108</t>
@@ -1076,7 +1076,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:43</t>
+    <t>2026-08-27 03:17:23</t>
   </si>
   <si>
     <t>PERF_LOD_109</t>
@@ -1085,7 +1085,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 03:51:53</t>
+    <t>2026-08-27 03:17:33</t>
   </si>
   <si>
     <t>PERF_LOD_110</t>
@@ -1094,7 +1094,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:03</t>
+    <t>2026-08-27 03:17:43</t>
   </si>
   <si>
     <t>PERF_LOD_111</t>
@@ -1103,7 +1103,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:13</t>
+    <t>2026-08-27 03:17:53</t>
   </si>
   <si>
     <t>PERF_LOD_112</t>
@@ -1112,7 +1112,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:23</t>
+    <t>2026-08-27 03:18:03</t>
   </si>
   <si>
     <t>PERF_LOD_113</t>
@@ -1121,7 +1121,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:33</t>
+    <t>2026-08-27 03:18:13</t>
   </si>
   <si>
     <t>PERF_LOD_114</t>
@@ -1130,7 +1130,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:43</t>
+    <t>2026-08-27 03:18:23</t>
   </si>
   <si>
     <t>PERF_LOD_115</t>
@@ -1139,7 +1139,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 03:52:53</t>
+    <t>2026-08-27 03:18:33</t>
   </si>
   <si>
     <t>PERF_LOD_116</t>
@@ -1148,7 +1148,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:03</t>
+    <t>2026-08-27 03:18:43</t>
   </si>
   <si>
     <t>PERF_LOD_117</t>
@@ -1157,7 +1157,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:13</t>
+    <t>2026-08-27 03:18:53</t>
   </si>
   <si>
     <t>PERF_LOD_118</t>
@@ -1166,7 +1166,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:23</t>
+    <t>2026-08-27 03:19:03</t>
   </si>
   <si>
     <t>PERF_LOD_119</t>
@@ -1175,7 +1175,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:33</t>
+    <t>2026-08-27 03:19:13</t>
   </si>
   <si>
     <t>PERF_LOD_120</t>
@@ -1184,7 +1184,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:43</t>
+    <t>2026-08-27 03:19:23</t>
   </si>
   <si>
     <t>PERF_LOD_121</t>
@@ -1196,7 +1196,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 03:53:53</t>
+    <t>2026-08-27 03:19:33</t>
   </si>
   <si>
     <t>PERF_LOD_122</t>
@@ -1205,7 +1205,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:03</t>
+    <t>2026-08-27 03:19:43</t>
   </si>
   <si>
     <t>PERF_LOD_123</t>
@@ -1214,7 +1214,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:13</t>
+    <t>2026-08-27 03:19:53</t>
   </si>
   <si>
     <t>PERF_LOD_124</t>
@@ -1223,7 +1223,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:23</t>
+    <t>2026-08-27 03:20:03</t>
   </si>
   <si>
     <t>PERF_LOD_125</t>
@@ -1232,7 +1232,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:33</t>
+    <t>2026-08-27 03:20:13</t>
   </si>
   <si>
     <t>PERF_LOD_126</t>
@@ -1241,7 +1241,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:43</t>
+    <t>2026-08-27 03:20:23</t>
   </si>
   <si>
     <t>PERF_LOD_127</t>
@@ -1250,7 +1250,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:54:53</t>
+    <t>2026-08-27 03:20:33</t>
   </si>
   <si>
     <t>PERF_LOD_128</t>
@@ -1259,7 +1259,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:03</t>
+    <t>2026-08-27 03:20:43</t>
   </si>
   <si>
     <t>PERF_LOD_129</t>
@@ -1268,7 +1268,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:13</t>
+    <t>2026-08-27 03:20:53</t>
   </si>
   <si>
     <t>PERF_LOD_130</t>
@@ -1277,7 +1277,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:23</t>
+    <t>2026-08-27 03:21:03</t>
   </si>
   <si>
     <t>PERF_LOD_131</t>
@@ -1286,7 +1286,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:33</t>
+    <t>2026-08-27 03:21:13</t>
   </si>
   <si>
     <t>PERF_LOD_132</t>
@@ -1295,7 +1295,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:43</t>
+    <t>2026-08-27 03:21:23</t>
   </si>
   <si>
     <t>PERF_LOD_133</t>
@@ -1304,7 +1304,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 03:55:53</t>
+    <t>2026-08-27 03:21:33</t>
   </si>
   <si>
     <t>PERF_LOD_134</t>
@@ -1313,7 +1313,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:03</t>
+    <t>2026-08-27 03:21:43</t>
   </si>
   <si>
     <t>PERF_LOD_135</t>
@@ -1322,7 +1322,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:13</t>
+    <t>2026-08-27 03:21:53</t>
   </si>
   <si>
     <t>PERF_LOD_136</t>
@@ -1331,7 +1331,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:23</t>
+    <t>2026-08-27 03:22:03</t>
   </si>
   <si>
     <t>PERF_LOD_137</t>
@@ -1340,7 +1340,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:33</t>
+    <t>2026-08-27 03:22:13</t>
   </si>
   <si>
     <t>PERF_LOD_138</t>
@@ -1349,7 +1349,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:43</t>
+    <t>2026-08-27 03:22:23</t>
   </si>
   <si>
     <t>PERF_LOD_139</t>
@@ -1358,7 +1358,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 03:56:53</t>
+    <t>2026-08-27 03:22:33</t>
   </si>
   <si>
     <t>PERF_LOD_140</t>
@@ -1367,7 +1367,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:03</t>
+    <t>2026-08-27 03:22:43</t>
   </si>
   <si>
     <t>PERF_LOD_141</t>
@@ -1376,7 +1376,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:13</t>
+    <t>2026-08-27 03:22:53</t>
   </si>
   <si>
     <t>PERF_LOD_142</t>
@@ -1385,7 +1385,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:23</t>
+    <t>2026-08-27 03:23:03</t>
   </si>
   <si>
     <t>PERF_LOD_143</t>
@@ -1394,7 +1394,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:33</t>
+    <t>2026-08-27 03:23:13</t>
   </si>
   <si>
     <t>PERF_LOD_144</t>
@@ -1403,7 +1403,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:43</t>
+    <t>2026-08-27 03:23:23</t>
   </si>
   <si>
     <t>PERF_LOD_145</t>
@@ -1412,7 +1412,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 03:57:53</t>
+    <t>2026-08-27 03:23:33</t>
   </si>
   <si>
     <t>PERF_LOD_146</t>
@@ -1421,7 +1421,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:03</t>
+    <t>2026-08-27 03:23:43</t>
   </si>
   <si>
     <t>PERF_LOD_147</t>
@@ -1430,7 +1430,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:13</t>
+    <t>2026-08-27 03:23:53</t>
   </si>
   <si>
     <t>PERF_LOD_148</t>
@@ -1439,7 +1439,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:23</t>
+    <t>2026-08-27 03:24:03</t>
   </si>
   <si>
     <t>PERF_LOD_149</t>
@@ -1448,7 +1448,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:33</t>
+    <t>2026-08-27 03:24:13</t>
   </si>
   <si>
     <t>PERF_LOD_150</t>
@@ -1457,7 +1457,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:43</t>
+    <t>2026-08-27 03:24:23</t>
   </si>
   <si>
     <t>PERF_LOD_151</t>
@@ -1469,7 +1469,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 03:58:53</t>
+    <t>2026-08-27 03:24:33</t>
   </si>
   <si>
     <t>PERF_LOD_152</t>
@@ -1478,7 +1478,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:03</t>
+    <t>2026-08-27 03:24:43</t>
   </si>
   <si>
     <t>PERF_LOD_153</t>
@@ -1487,7 +1487,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:13</t>
+    <t>2026-08-27 03:24:53</t>
   </si>
   <si>
     <t>PERF_LOD_154</t>
@@ -1496,7 +1496,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:23</t>
+    <t>2026-08-27 03:25:03</t>
   </si>
   <si>
     <t>PERF_LOD_155</t>
@@ -1505,7 +1505,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:33</t>
+    <t>2026-08-27 03:25:13</t>
   </si>
   <si>
     <t>PERF_LOD_156</t>
@@ -1514,7 +1514,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:43</t>
+    <t>2026-08-27 03:25:23</t>
   </si>
   <si>
     <t>PERF_LOD_157</t>
@@ -1523,7 +1523,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 03:59:53</t>
+    <t>2026-08-27 03:25:33</t>
   </si>
   <si>
     <t>PERF_LOD_158</t>
@@ -1532,7 +1532,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:03</t>
+    <t>2026-08-27 03:25:43</t>
   </si>
   <si>
     <t>PERF_LOD_159</t>
@@ -1541,7 +1541,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:13</t>
+    <t>2026-08-27 03:25:53</t>
   </si>
   <si>
     <t>PERF_LOD_160</t>
@@ -1550,7 +1550,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:23</t>
+    <t>2026-08-27 03:26:03</t>
   </si>
   <si>
     <t>PERF_LOD_161</t>
@@ -1559,7 +1559,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:33</t>
+    <t>2026-08-27 03:26:13</t>
   </si>
   <si>
     <t>PERF_LOD_162</t>
@@ -1568,7 +1568,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:43</t>
+    <t>2026-08-27 03:26:23</t>
   </si>
   <si>
     <t>PERF_LOD_163</t>
@@ -1577,7 +1577,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 04:00:53</t>
+    <t>2026-08-27 03:26:33</t>
   </si>
   <si>
     <t>PERF_LOD_164</t>
@@ -1586,7 +1586,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:03</t>
+    <t>2026-08-27 03:26:43</t>
   </si>
   <si>
     <t>PERF_LOD_165</t>
@@ -1595,7 +1595,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:13</t>
+    <t>2026-08-27 03:26:53</t>
   </si>
   <si>
     <t>PERF_LOD_166</t>
@@ -1604,7 +1604,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:23</t>
+    <t>2026-08-27 03:27:03</t>
   </si>
   <si>
     <t>PERF_LOD_167</t>
@@ -1613,7 +1613,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:33</t>
+    <t>2026-08-27 03:27:13</t>
   </si>
   <si>
     <t>PERF_LOD_168</t>
@@ -1622,7 +1622,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:43</t>
+    <t>2026-08-27 03:27:23</t>
   </si>
   <si>
     <t>PERF_LOD_169</t>
@@ -1631,7 +1631,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 04:01:53</t>
+    <t>2026-08-27 03:27:33</t>
   </si>
   <si>
     <t>PERF_LOD_170</t>
@@ -1640,7 +1640,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:03</t>
+    <t>2026-08-27 03:27:43</t>
   </si>
   <si>
     <t>PERF_LOD_171</t>
@@ -1649,7 +1649,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:13</t>
+    <t>2026-08-27 03:27:53</t>
   </si>
   <si>
     <t>PERF_LOD_172</t>
@@ -1658,7 +1658,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:23</t>
+    <t>2026-08-27 03:28:03</t>
   </si>
   <si>
     <t>PERF_LOD_173</t>
@@ -1667,7 +1667,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:33</t>
+    <t>2026-08-27 03:28:13</t>
   </si>
   <si>
     <t>PERF_LOD_174</t>
@@ -1676,7 +1676,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:43</t>
+    <t>2026-08-27 03:28:23</t>
   </si>
   <si>
     <t>PERF_LOD_175</t>
@@ -1685,7 +1685,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 04:02:53</t>
+    <t>2026-08-27 03:28:33</t>
   </si>
   <si>
     <t>PERF_LOD_176</t>
@@ -1694,7 +1694,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:03</t>
+    <t>2026-08-27 03:28:43</t>
   </si>
   <si>
     <t>PERF_LOD_177</t>
@@ -1703,7 +1703,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:13</t>
+    <t>2026-08-27 03:28:53</t>
   </si>
   <si>
     <t>PERF_LOD_178</t>
@@ -1712,7 +1712,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:23</t>
+    <t>2026-08-27 03:29:03</t>
   </si>
   <si>
     <t>PERF_LOD_179</t>
@@ -1721,7 +1721,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:33</t>
+    <t>2026-08-27 03:29:13</t>
   </si>
   <si>
     <t>PERF_LOD_180</t>
@@ -1730,7 +1730,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:43</t>
+    <t>2026-08-27 03:29:23</t>
   </si>
   <si>
     <t>PERF_LOD_181</t>
@@ -1742,7 +1742,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 04:03:53</t>
+    <t>2026-08-27 03:29:33</t>
   </si>
   <si>
     <t>PERF_LOD_182</t>
@@ -1751,7 +1751,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:03</t>
+    <t>2026-08-27 03:29:43</t>
   </si>
   <si>
     <t>PERF_LOD_183</t>
@@ -1760,7 +1760,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:13</t>
+    <t>2026-08-27 03:29:53</t>
   </si>
   <si>
     <t>PERF_LOD_184</t>
@@ -1769,7 +1769,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:23</t>
+    <t>2026-08-27 03:30:03</t>
   </si>
   <si>
     <t>PERF_LOD_185</t>
@@ -1778,7 +1778,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:33</t>
+    <t>2026-08-27 03:30:13</t>
   </si>
   <si>
     <t>PERF_LOD_186</t>
@@ -1787,7 +1787,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:43</t>
+    <t>2026-08-27 03:30:23</t>
   </si>
   <si>
     <t>PERF_LOD_187</t>
@@ -1796,7 +1796,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 04:04:53</t>
+    <t>2026-08-27 03:30:33</t>
   </si>
   <si>
     <t>PERF_LOD_188</t>
@@ -1805,7 +1805,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:03</t>
+    <t>2026-08-27 03:30:43</t>
   </si>
   <si>
     <t>PERF_LOD_189</t>
@@ -1814,7 +1814,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:13</t>
+    <t>2026-08-27 03:30:53</t>
   </si>
   <si>
     <t>PERF_LOD_190</t>
@@ -1823,7 +1823,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:23</t>
+    <t>2026-08-27 03:31:03</t>
   </si>
   <si>
     <t>PERF_LOD_191</t>
@@ -1832,7 +1832,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:33</t>
+    <t>2026-08-27 03:31:13</t>
   </si>
   <si>
     <t>PERF_LOD_192</t>
@@ -1841,7 +1841,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:43</t>
+    <t>2026-08-27 03:31:23</t>
   </si>
   <si>
     <t>PERF_LOD_193</t>
@@ -1850,7 +1850,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 04:05:53</t>
+    <t>2026-08-27 03:31:33</t>
   </si>
   <si>
     <t>PERF_LOD_194</t>
@@ -1859,7 +1859,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:03</t>
+    <t>2026-08-27 03:31:43</t>
   </si>
   <si>
     <t>PERF_LOD_195</t>
@@ -1868,7 +1868,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:13</t>
+    <t>2026-08-27 03:31:53</t>
   </si>
   <si>
     <t>PERF_LOD_196</t>
@@ -1877,7 +1877,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:23</t>
+    <t>2026-08-27 03:32:03</t>
   </si>
   <si>
     <t>PERF_LOD_197</t>
@@ -1886,7 +1886,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:33</t>
+    <t>2026-08-27 03:32:13</t>
   </si>
   <si>
     <t>PERF_LOD_198</t>
@@ -1895,7 +1895,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:43</t>
+    <t>2026-08-27 03:32:23</t>
   </si>
   <si>
     <t>PERF_LOD_199</t>
@@ -1904,7 +1904,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 04:06:53</t>
+    <t>2026-08-27 03:32:33</t>
   </si>
   <si>
     <t>PERF_LOD_200</t>
@@ -1913,7 +1913,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:03</t>
+    <t>2026-08-27 03:32:43</t>
   </si>
   <si>
     <t>PERF_LOD_201</t>
@@ -1922,7 +1922,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:13</t>
+    <t>2026-08-27 03:32:53</t>
   </si>
   <si>
     <t>PERF_LOD_202</t>
@@ -1931,7 +1931,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:23</t>
+    <t>2026-08-27 03:33:03</t>
   </si>
   <si>
     <t>PERF_LOD_203</t>
@@ -1940,7 +1940,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:33</t>
+    <t>2026-08-27 03:33:13</t>
   </si>
   <si>
     <t>PERF_LOD_204</t>
@@ -1949,7 +1949,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:43</t>
+    <t>2026-08-27 03:33:23</t>
   </si>
   <si>
     <t>PERF_LOD_205</t>
@@ -1958,7 +1958,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 04:07:53</t>
+    <t>2026-08-27 03:33:33</t>
   </si>
   <si>
     <t>PERF_LOD_206</t>
@@ -1967,7 +1967,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:03</t>
+    <t>2026-08-27 03:33:43</t>
   </si>
   <si>
     <t>PERF_LOD_207</t>
@@ -1976,7 +1976,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:13</t>
+    <t>2026-08-27 03:33:53</t>
   </si>
   <si>
     <t>PERF_LOD_208</t>
@@ -1985,7 +1985,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:23</t>
+    <t>2026-08-27 03:34:03</t>
   </si>
   <si>
     <t>PERF_LOD_209</t>
@@ -1994,7 +1994,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:33</t>
+    <t>2026-08-27 03:34:13</t>
   </si>
   <si>
     <t>PERF_LOD_210</t>
@@ -2003,7 +2003,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:43</t>
+    <t>2026-08-27 03:34:23</t>
   </si>
   <si>
     <t>PERF_LOD_211</t>
@@ -2015,7 +2015,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 04:08:53</t>
+    <t>2026-08-27 03:34:33</t>
   </si>
   <si>
     <t>PERF_LOD_212</t>
@@ -2024,7 +2024,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:03</t>
+    <t>2026-08-27 03:34:43</t>
   </si>
   <si>
     <t>PERF_LOD_213</t>
@@ -2033,7 +2033,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:13</t>
+    <t>2026-08-27 03:34:53</t>
   </si>
   <si>
     <t>PERF_LOD_214</t>
@@ -2042,7 +2042,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:23</t>
+    <t>2026-08-27 03:35:03</t>
   </si>
   <si>
     <t>PERF_LOD_215</t>
@@ -2051,7 +2051,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:33</t>
+    <t>2026-08-27 03:35:13</t>
   </si>
   <si>
     <t>PERF_LOD_216</t>
@@ -2060,7 +2060,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:43</t>
+    <t>2026-08-27 03:35:23</t>
   </si>
   <si>
     <t>PERF_LOD_217</t>
@@ -2069,7 +2069,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 04:09:53</t>
+    <t>2026-08-27 03:35:33</t>
   </si>
   <si>
     <t>PERF_LOD_218</t>
@@ -2078,7 +2078,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:03</t>
+    <t>2026-08-27 03:35:43</t>
   </si>
   <si>
     <t>PERF_LOD_219</t>
@@ -2087,7 +2087,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:13</t>
+    <t>2026-08-27 03:35:53</t>
   </si>
   <si>
     <t>PERF_LOD_220</t>
@@ -2096,7 +2096,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:23</t>
+    <t>2026-08-27 03:36:03</t>
   </si>
   <si>
     <t>PERF_LOD_221</t>
@@ -2105,7 +2105,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:33</t>
+    <t>2026-08-27 03:36:13</t>
   </si>
   <si>
     <t>PERF_LOD_222</t>
@@ -2114,7 +2114,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:43</t>
+    <t>2026-08-27 03:36:23</t>
   </si>
   <si>
     <t>PERF_LOD_223</t>
@@ -2123,7 +2123,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 04:10:53</t>
+    <t>2026-08-27 03:36:33</t>
   </si>
   <si>
     <t>PERF_LOD_224</t>
@@ -2132,7 +2132,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:03</t>
+    <t>2026-08-27 03:36:43</t>
   </si>
   <si>
     <t>PERF_LOD_225</t>
@@ -2141,7 +2141,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:13</t>
+    <t>2026-08-27 03:36:53</t>
   </si>
   <si>
     <t>PERF_LOD_226</t>
@@ -2150,7 +2150,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:23</t>
+    <t>2026-08-27 03:37:03</t>
   </si>
   <si>
     <t>PERF_LOD_227</t>
@@ -2159,7 +2159,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:33</t>
+    <t>2026-08-27 03:37:13</t>
   </si>
   <si>
     <t>PERF_LOD_228</t>
@@ -2168,7 +2168,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:43</t>
+    <t>2026-08-27 03:37:23</t>
   </si>
   <si>
     <t>PERF_LOD_229</t>
@@ -2177,7 +2177,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 04:11:53</t>
+    <t>2026-08-27 03:37:33</t>
   </si>
   <si>
     <t>PERF_LOD_230</t>
@@ -2186,7 +2186,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:03</t>
+    <t>2026-08-27 03:37:43</t>
   </si>
   <si>
     <t>PERF_LOD_231</t>
@@ -2195,7 +2195,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:13</t>
+    <t>2026-08-27 03:37:53</t>
   </si>
   <si>
     <t>PERF_LOD_232</t>
@@ -2204,7 +2204,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:23</t>
+    <t>2026-08-27 03:38:03</t>
   </si>
   <si>
     <t>PERF_LOD_233</t>
@@ -2213,7 +2213,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:33</t>
+    <t>2026-08-27 03:38:13</t>
   </si>
   <si>
     <t>PERF_LOD_234</t>
@@ -2222,7 +2222,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:43</t>
+    <t>2026-08-27 03:38:23</t>
   </si>
   <si>
     <t>PERF_LOD_235</t>
@@ -2231,7 +2231,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 04:12:53</t>
+    <t>2026-08-27 03:38:33</t>
   </si>
   <si>
     <t>PERF_LOD_236</t>
@@ -2240,7 +2240,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:03</t>
+    <t>2026-08-27 03:38:43</t>
   </si>
   <si>
     <t>PERF_LOD_237</t>
@@ -2249,7 +2249,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:13</t>
+    <t>2026-08-27 03:38:53</t>
   </si>
   <si>
     <t>PERF_LOD_238</t>
@@ -2258,7 +2258,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:23</t>
+    <t>2026-08-27 03:39:03</t>
   </si>
   <si>
     <t>PERF_LOD_239</t>
@@ -2267,7 +2267,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:33</t>
+    <t>2026-08-27 03:39:13</t>
   </si>
   <si>
     <t>PERF_LOD_240</t>
@@ -2276,7 +2276,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:43</t>
+    <t>2026-08-27 03:39:23</t>
   </si>
   <si>
     <t>PERF_LOD_241</t>
@@ -2288,7 +2288,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 04:13:53</t>
+    <t>2026-08-27 03:39:33</t>
   </si>
   <si>
     <t>PERF_LOD_242</t>
@@ -2297,7 +2297,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:03</t>
+    <t>2026-08-27 03:39:43</t>
   </si>
   <si>
     <t>PERF_LOD_243</t>
@@ -2306,7 +2306,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:13</t>
+    <t>2026-08-27 03:39:53</t>
   </si>
   <si>
     <t>PERF_LOD_244</t>
@@ -2315,7 +2315,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:23</t>
+    <t>2026-08-27 03:40:03</t>
   </si>
   <si>
     <t>PERF_LOD_245</t>
@@ -2324,7 +2324,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:33</t>
+    <t>2026-08-27 03:40:13</t>
   </si>
   <si>
     <t>PERF_LOD_246</t>
@@ -2333,7 +2333,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:43</t>
+    <t>2026-08-27 03:40:23</t>
   </si>
   <si>
     <t>PERF_LOD_247</t>
@@ -2342,7 +2342,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 04:14:53</t>
+    <t>2026-08-27 03:40:33</t>
   </si>
   <si>
     <t>PERF_LOD_248</t>
@@ -2351,7 +2351,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:03</t>
+    <t>2026-08-27 03:40:43</t>
   </si>
   <si>
     <t>PERF_LOD_249</t>
@@ -2360,7 +2360,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:13</t>
+    <t>2026-08-27 03:40:53</t>
   </si>
   <si>
     <t>PERF_LOD_250</t>
@@ -2369,7 +2369,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:23</t>
+    <t>2026-08-27 03:41:03</t>
   </si>
   <si>
     <t>PERF_LOD_251</t>
@@ -2378,7 +2378,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:33</t>
+    <t>2026-08-27 03:41:13</t>
   </si>
   <si>
     <t>PERF_LOD_252</t>
@@ -2387,7 +2387,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:43</t>
+    <t>2026-08-27 03:41:23</t>
   </si>
   <si>
     <t>PERF_LOD_253</t>
@@ -2396,7 +2396,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 04:15:53</t>
+    <t>2026-08-27 03:41:33</t>
   </si>
   <si>
     <t>PERF_LOD_254</t>
@@ -2405,7 +2405,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:03</t>
+    <t>2026-08-27 03:41:43</t>
   </si>
   <si>
     <t>PERF_LOD_255</t>
@@ -2414,7 +2414,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:13</t>
+    <t>2026-08-27 03:41:53</t>
   </si>
   <si>
     <t>PERF_LOD_256</t>
@@ -2423,7 +2423,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:23</t>
+    <t>2026-08-27 03:42:03</t>
   </si>
   <si>
     <t>PERF_LOD_257</t>
@@ -2432,7 +2432,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:33</t>
+    <t>2026-08-27 03:42:13</t>
   </si>
   <si>
     <t>PERF_LOD_258</t>
@@ -2441,7 +2441,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:43</t>
+    <t>2026-08-27 03:42:23</t>
   </si>
   <si>
     <t>PERF_LOD_259</t>
@@ -2450,7 +2450,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 04:16:53</t>
+    <t>2026-08-27 03:42:33</t>
   </si>
   <si>
     <t>PERF_LOD_260</t>
@@ -2459,7 +2459,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:03</t>
+    <t>2026-08-27 03:42:43</t>
   </si>
   <si>
     <t>PERF_LOD_261</t>
@@ -2468,7 +2468,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:13</t>
+    <t>2026-08-27 03:42:53</t>
   </si>
   <si>
     <t>PERF_LOD_262</t>
@@ -2477,7 +2477,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:23</t>
+    <t>2026-08-27 03:43:03</t>
   </si>
   <si>
     <t>PERF_LOD_263</t>
@@ -2486,7 +2486,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:33</t>
+    <t>2026-08-27 03:43:13</t>
   </si>
   <si>
     <t>PERF_LOD_264</t>
@@ -2495,7 +2495,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:43</t>
+    <t>2026-08-27 03:43:23</t>
   </si>
   <si>
     <t>PERF_LOD_265</t>
@@ -2504,7 +2504,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 04:17:53</t>
+    <t>2026-08-27 03:43:33</t>
   </si>
   <si>
     <t>PERF_LOD_266</t>
@@ -2513,7 +2513,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:03</t>
+    <t>2026-08-27 03:43:43</t>
   </si>
   <si>
     <t>PERF_LOD_267</t>
@@ -2522,7 +2522,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:13</t>
+    <t>2026-08-27 03:43:53</t>
   </si>
   <si>
     <t>PERF_LOD_268</t>
@@ -2531,7 +2531,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:23</t>
+    <t>2026-08-27 03:44:03</t>
   </si>
   <si>
     <t>PERF_LOD_269</t>
@@ -2540,7 +2540,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:33</t>
+    <t>2026-08-27 03:44:13</t>
   </si>
   <si>
     <t>PERF_LOD_270</t>
@@ -2549,7 +2549,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:43</t>
+    <t>2026-08-27 03:44:23</t>
   </si>
   <si>
     <t>PERF_LOD_271</t>
@@ -2561,7 +2561,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-26 04:18:53</t>
+    <t>2026-08-27 03:44:33</t>
   </si>
   <si>
     <t>PERF_LOD_272</t>
@@ -2570,7 +2570,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:03</t>
+    <t>2026-08-27 03:44:43</t>
   </si>
   <si>
     <t>PERF_LOD_273</t>
@@ -2579,7 +2579,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:13</t>
+    <t>2026-08-27 03:44:53</t>
   </si>
   <si>
     <t>PERF_LOD_274</t>
@@ -2588,7 +2588,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:23</t>
+    <t>2026-08-27 03:45:03</t>
   </si>
   <si>
     <t>PERF_LOD_275</t>
@@ -2597,7 +2597,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:33</t>
+    <t>2026-08-27 03:45:13</t>
   </si>
   <si>
     <t>PERF_LOD_276</t>
@@ -2606,7 +2606,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:43</t>
+    <t>2026-08-27 03:45:23</t>
   </si>
   <si>
     <t>PERF_LOD_277</t>
@@ -2615,7 +2615,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-26 04:19:53</t>
+    <t>2026-08-27 03:45:33</t>
   </si>
   <si>
     <t>PERF_LOD_278</t>
@@ -2624,7 +2624,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:03</t>
+    <t>2026-08-27 03:45:43</t>
   </si>
   <si>
     <t>PERF_LOD_279</t>
@@ -2633,7 +2633,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:13</t>
+    <t>2026-08-27 03:45:53</t>
   </si>
   <si>
     <t>PERF_LOD_280</t>
@@ -2642,7 +2642,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:23</t>
+    <t>2026-08-27 03:46:03</t>
   </si>
   <si>
     <t>PERF_LOD_281</t>
@@ -2651,7 +2651,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:33</t>
+    <t>2026-08-27 03:46:13</t>
   </si>
   <si>
     <t>PERF_LOD_282</t>
@@ -2660,7 +2660,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:43</t>
+    <t>2026-08-27 03:46:23</t>
   </si>
   <si>
     <t>PERF_LOD_283</t>
@@ -2669,7 +2669,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-26 04:20:53</t>
+    <t>2026-08-27 03:46:33</t>
   </si>
   <si>
     <t>PERF_LOD_284</t>
@@ -2678,7 +2678,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:03</t>
+    <t>2026-08-27 03:46:43</t>
   </si>
   <si>
     <t>PERF_LOD_285</t>
@@ -2687,7 +2687,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:13</t>
+    <t>2026-08-27 03:46:53</t>
   </si>
   <si>
     <t>PERF_LOD_286</t>
@@ -2696,7 +2696,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:23</t>
+    <t>2026-08-27 03:47:03</t>
   </si>
   <si>
     <t>PERF_LOD_287</t>
@@ -2705,7 +2705,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:33</t>
+    <t>2026-08-27 03:47:13</t>
   </si>
   <si>
     <t>PERF_LOD_288</t>
@@ -2714,7 +2714,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:43</t>
+    <t>2026-08-27 03:47:23</t>
   </si>
   <si>
     <t>PERF_LOD_289</t>
@@ -2723,7 +2723,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-26 04:21:53</t>
+    <t>2026-08-27 03:47:33</t>
   </si>
   <si>
     <t>PERF_LOD_290</t>
@@ -2732,7 +2732,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:03</t>
+    <t>2026-08-27 03:47:43</t>
   </si>
   <si>
     <t>PERF_LOD_291</t>
@@ -2741,7 +2741,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:13</t>
+    <t>2026-08-27 03:47:53</t>
   </si>
   <si>
     <t>PERF_LOD_292</t>
@@ -2750,7 +2750,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:23</t>
+    <t>2026-08-27 03:48:03</t>
   </si>
   <si>
     <t>PERF_LOD_293</t>
@@ -2759,7 +2759,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:33</t>
+    <t>2026-08-27 03:48:13</t>
   </si>
   <si>
     <t>PERF_LOD_294</t>
@@ -2768,7 +2768,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:43</t>
+    <t>2026-08-27 03:48:23</t>
   </si>
   <si>
     <t>PERF_LOD_295</t>
@@ -2777,7 +2777,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-26 04:22:53</t>
+    <t>2026-08-27 03:48:33</t>
   </si>
   <si>
     <t>PERF_LOD_296</t>
@@ -2786,7 +2786,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-26 04:23:03</t>
+    <t>2026-08-27 03:48:43</t>
   </si>
   <si>
     <t>PERF_LOD_297</t>
@@ -2795,7 +2795,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-26 04:23:13</t>
+    <t>2026-08-27 03:48:53</t>
   </si>
   <si>
     <t>PERF_LOD_298</t>
@@ -2804,7 +2804,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-26 04:23:23</t>
+    <t>2026-08-27 03:49:03</t>
   </si>
   <si>
     <t>PERF_LOD_299</t>
@@ -2813,7 +2813,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-26 04:23:33</t>
+    <t>2026-08-27 03:49:13</t>
   </si>
   <si>
     <t>PERF_LOD_300</t>
@@ -2822,7 +2822,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-26 04:23:43</t>
+    <t>2026-08-27 03:49:23</t>
   </si>
 </sst>
 </file>
@@ -3375,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>30</v>
@@ -3395,7 +3395,7 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -3415,7 +3415,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="3">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -3455,7 +3455,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="3">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>42</v>
@@ -3475,7 +3475,7 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F7" t="s">
         <v>45</v>
@@ -3495,7 +3495,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="3">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>48</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
@@ -3535,7 +3535,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>54</v>
@@ -3555,7 +3555,7 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -3575,7 +3575,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>63</v>
@@ -3615,7 +3615,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>66</v>
@@ -3635,7 +3635,7 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F15" t="s">
         <v>69</v>
@@ -3655,7 +3655,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>72</v>
@@ -3675,7 +3675,7 @@
         <v>29</v>
       </c>
       <c r="E17">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
@@ -3695,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>78</v>
@@ -3715,7 +3715,7 @@
         <v>29</v>
       </c>
       <c r="E19">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F19" t="s">
         <v>81</v>
@@ -3755,7 +3755,7 @@
         <v>29</v>
       </c>
       <c r="E21">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F21" t="s">
         <v>87</v>
@@ -3775,7 +3775,7 @@
         <v>29</v>
       </c>
       <c r="E22" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>90</v>
@@ -3795,7 +3795,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F23" t="s">
         <v>93</v>
@@ -3815,7 +3815,7 @@
         <v>29</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>96</v>
@@ -3835,7 +3835,7 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F25" t="s">
         <v>99</v>
@@ -3855,7 +3855,7 @@
         <v>29</v>
       </c>
       <c r="E26" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>102</v>
@@ -3875,7 +3875,7 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F27" t="s">
         <v>105</v>
@@ -3895,7 +3895,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>108</v>
@@ -3915,7 +3915,7 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F29" t="s">
         <v>111</v>
@@ -3935,7 +3935,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>114</v>
@@ -3955,7 +3955,7 @@
         <v>29</v>
       </c>
       <c r="E31">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F31" t="s">
         <v>117</v>
@@ -3975,7 +3975,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>121</v>
@@ -3995,7 +3995,7 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
         <v>124</v>
@@ -4015,7 +4015,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>127</v>
@@ -4035,7 +4035,7 @@
         <v>29</v>
       </c>
       <c r="E35">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F35" t="s">
         <v>130</v>
@@ -4055,7 +4055,7 @@
         <v>29</v>
       </c>
       <c r="E36" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>133</v>
@@ -4075,7 +4075,7 @@
         <v>29</v>
       </c>
       <c r="E37">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F37" t="s">
         <v>136</v>
@@ -4095,7 +4095,7 @@
         <v>29</v>
       </c>
       <c r="E38" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>139</v>
@@ -4115,7 +4115,7 @@
         <v>29</v>
       </c>
       <c r="E39">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F39" t="s">
         <v>142</v>
@@ -4135,7 +4135,7 @@
         <v>29</v>
       </c>
       <c r="E40" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>145</v>
@@ -4155,7 +4155,7 @@
         <v>29</v>
       </c>
       <c r="E41">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F41" t="s">
         <v>148</v>
@@ -4175,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="E42" s="3">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>151</v>
@@ -4215,7 +4215,7 @@
         <v>29</v>
       </c>
       <c r="E44" s="3">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>157</v>
@@ -4235,7 +4235,7 @@
         <v>29</v>
       </c>
       <c r="E45">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="F45" t="s">
         <v>160</v>
@@ -4255,7 +4255,7 @@
         <v>29</v>
       </c>
       <c r="E46" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>163</v>
@@ -4275,7 +4275,7 @@
         <v>29</v>
       </c>
       <c r="E47">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F47" t="s">
         <v>166</v>
@@ -4295,7 +4295,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="3">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>169</v>
@@ -4315,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="E49">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F49" t="s">
         <v>172</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>175</v>
@@ -4355,7 +4355,7 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F51" t="s">
         <v>178</v>
@@ -4395,7 +4395,7 @@
         <v>29</v>
       </c>
       <c r="E53">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="F53" t="s">
         <v>184</v>
@@ -4415,7 +4415,7 @@
         <v>29</v>
       </c>
       <c r="E54" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>187</v>
@@ -4435,7 +4435,7 @@
         <v>29</v>
       </c>
       <c r="E55">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F55" t="s">
         <v>190</v>
@@ -4455,7 +4455,7 @@
         <v>29</v>
       </c>
       <c r="E56" s="3">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>193</v>
@@ -4475,7 +4475,7 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="F57" t="s">
         <v>196</v>
@@ -4495,7 +4495,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>199</v>
@@ -4515,7 +4515,7 @@
         <v>29</v>
       </c>
       <c r="E59">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F59" t="s">
         <v>202</v>
@@ -4535,7 +4535,7 @@
         <v>29</v>
       </c>
       <c r="E60" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>205</v>
@@ -4555,7 +4555,7 @@
         <v>29</v>
       </c>
       <c r="E61">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="F61" t="s">
         <v>208</v>
@@ -4575,7 +4575,7 @@
         <v>29</v>
       </c>
       <c r="E62" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>212</v>
@@ -4595,7 +4595,7 @@
         <v>29</v>
       </c>
       <c r="E63">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F63" t="s">
         <v>215</v>
@@ -4615,7 +4615,7 @@
         <v>29</v>
       </c>
       <c r="E64" s="3">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>218</v>
@@ -4635,7 +4635,7 @@
         <v>29</v>
       </c>
       <c r="E65">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F65" t="s">
         <v>221</v>
@@ -4655,7 +4655,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>224</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="E67">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F67" t="s">
         <v>227</v>
@@ -4695,7 +4695,7 @@
         <v>29</v>
       </c>
       <c r="E68" s="3">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>230</v>
@@ -4715,7 +4715,7 @@
         <v>29</v>
       </c>
       <c r="E69">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F69" t="s">
         <v>233</v>
@@ -4735,7 +4735,7 @@
         <v>29</v>
       </c>
       <c r="E70" s="3">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>236</v>
@@ -4755,7 +4755,7 @@
         <v>29</v>
       </c>
       <c r="E71">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F71" t="s">
         <v>239</v>
@@ -4775,7 +4775,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>242</v>
@@ -4795,7 +4795,7 @@
         <v>29</v>
       </c>
       <c r="E73">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="F73" t="s">
         <v>245</v>
@@ -4815,7 +4815,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>248</v>
@@ -4835,7 +4835,7 @@
         <v>29</v>
       </c>
       <c r="E75">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F75" t="s">
         <v>251</v>
@@ -4855,7 +4855,7 @@
         <v>29</v>
       </c>
       <c r="E76" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>254</v>
@@ -4875,7 +4875,7 @@
         <v>29</v>
       </c>
       <c r="E77">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F77" t="s">
         <v>257</v>
@@ -4895,7 +4895,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>260</v>
@@ -4915,7 +4915,7 @@
         <v>29</v>
       </c>
       <c r="E79">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F79" t="s">
         <v>263</v>
@@ -4935,7 +4935,7 @@
         <v>29</v>
       </c>
       <c r="E80" s="3">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>266</v>
@@ -4975,7 +4975,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="3">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>272</v>
@@ -4995,7 +4995,7 @@
         <v>29</v>
       </c>
       <c r="E83">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F83" t="s">
         <v>275</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="E84" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>278</v>
@@ -5035,7 +5035,7 @@
         <v>29</v>
       </c>
       <c r="E85">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F85" t="s">
         <v>281</v>
@@ -5055,7 +5055,7 @@
         <v>29</v>
       </c>
       <c r="E86" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>284</v>
@@ -5075,7 +5075,7 @@
         <v>29</v>
       </c>
       <c r="E87">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F87" t="s">
         <v>287</v>
@@ -5095,7 +5095,7 @@
         <v>29</v>
       </c>
       <c r="E88" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>290</v>
@@ -5115,7 +5115,7 @@
         <v>29</v>
       </c>
       <c r="E89">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F89" t="s">
         <v>293</v>
@@ -5135,7 +5135,7 @@
         <v>29</v>
       </c>
       <c r="E90" s="3">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>296</v>
@@ -5155,7 +5155,7 @@
         <v>29</v>
       </c>
       <c r="E91">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F91" t="s">
         <v>299</v>
@@ -5175,7 +5175,7 @@
         <v>29</v>
       </c>
       <c r="E92" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>303</v>
@@ -5195,7 +5195,7 @@
         <v>29</v>
       </c>
       <c r="E93">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F93" t="s">
         <v>306</v>
@@ -5215,7 +5215,7 @@
         <v>29</v>
       </c>
       <c r="E94" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>309</v>
@@ -5235,7 +5235,7 @@
         <v>29</v>
       </c>
       <c r="E95">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F95" t="s">
         <v>312</v>
@@ -5255,7 +5255,7 @@
         <v>29</v>
       </c>
       <c r="E96" s="3">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>315</v>
@@ -5275,7 +5275,7 @@
         <v>29</v>
       </c>
       <c r="E97">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s">
         <v>318</v>
@@ -5315,7 +5315,7 @@
         <v>29</v>
       </c>
       <c r="E99">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="F99" t="s">
         <v>324</v>
@@ -5335,7 +5335,7 @@
         <v>29</v>
       </c>
       <c r="E100" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>327</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="E101">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F101" t="s">
         <v>330</v>
@@ -5375,7 +5375,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="3">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>333</v>
@@ -5395,7 +5395,7 @@
         <v>29</v>
       </c>
       <c r="E103">
-        <v>7</v>
+        <v>20</v>
       </c>
       <c r="F103" t="s">
         <v>336</v>
@@ -5415,7 +5415,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="3">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>339</v>
@@ -5435,7 +5435,7 @@
         <v>29</v>
       </c>
       <c r="E105">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F105" t="s">
         <v>342</v>
@@ -5455,7 +5455,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>345</v>
@@ -5475,7 +5475,7 @@
         <v>29</v>
       </c>
       <c r="E107">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F107" t="s">
         <v>348</v>
@@ -5495,7 +5495,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="3">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>351</v>
@@ -5515,7 +5515,7 @@
         <v>29</v>
       </c>
       <c r="E109">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F109" t="s">
         <v>354</v>
@@ -5535,7 +5535,7 @@
         <v>29</v>
       </c>
       <c r="E110" s="3">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>357</v>
@@ -5555,7 +5555,7 @@
         <v>29</v>
       </c>
       <c r="E111">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F111" t="s">
         <v>360</v>
@@ -5575,7 +5575,7 @@
         <v>29</v>
       </c>
       <c r="E112" s="3">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>363</v>
@@ -5615,7 +5615,7 @@
         <v>29</v>
       </c>
       <c r="E114" s="3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F114" s="3" t="s">
         <v>369</v>
@@ -5635,7 +5635,7 @@
         <v>29</v>
       </c>
       <c r="E115">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s">
         <v>372</v>
@@ -5655,7 +5655,7 @@
         <v>29</v>
       </c>
       <c r="E116" s="3">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>375</v>
@@ -5675,7 +5675,7 @@
         <v>29</v>
       </c>
       <c r="E117">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F117" t="s">
         <v>378</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="E118" s="3">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>381</v>
@@ -5715,7 +5715,7 @@
         <v>29</v>
       </c>
       <c r="E119">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F119" t="s">
         <v>384</v>
@@ -5755,7 +5755,7 @@
         <v>29</v>
       </c>
       <c r="E121">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F121" t="s">
         <v>390</v>
@@ -5775,7 +5775,7 @@
         <v>29</v>
       </c>
       <c r="E122" s="3">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>394</v>
@@ -5795,7 +5795,7 @@
         <v>29</v>
       </c>
       <c r="E123">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F123" t="s">
         <v>397</v>
@@ -5815,7 +5815,7 @@
         <v>29</v>
       </c>
       <c r="E124" s="3">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F124" s="3" t="s">
         <v>400</v>
@@ -5835,7 +5835,7 @@
         <v>29</v>
       </c>
       <c r="E125">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="F125" t="s">
         <v>403</v>
@@ -5855,7 +5855,7 @@
         <v>29</v>
       </c>
       <c r="E126" s="3">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>406</v>
@@ -5875,7 +5875,7 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F127" t="s">
         <v>409</v>
@@ -5895,7 +5895,7 @@
         <v>29</v>
       </c>
       <c r="E128" s="3">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="F128" s="3" t="s">
         <v>412</v>
@@ -5915,7 +5915,7 @@
         <v>29</v>
       </c>
       <c r="E129">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F129" t="s">
         <v>415</v>
@@ -5955,7 +5955,7 @@
         <v>29</v>
       </c>
       <c r="E131">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="F131" t="s">
         <v>421</v>
@@ -5975,7 +5975,7 @@
         <v>29</v>
       </c>
       <c r="E132" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>424</v>
@@ -5995,7 +5995,7 @@
         <v>29</v>
       </c>
       <c r="E133">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F133" t="s">
         <v>427</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="E135">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F135" t="s">
         <v>433</v>
@@ -6055,7 +6055,7 @@
         <v>29</v>
       </c>
       <c r="E136" s="3">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>436</v>
@@ -6095,7 +6095,7 @@
         <v>29</v>
       </c>
       <c r="E138" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>442</v>
@@ -6115,7 +6115,7 @@
         <v>29</v>
       </c>
       <c r="E139">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F139" t="s">
         <v>445</v>
@@ -6135,7 +6135,7 @@
         <v>29</v>
       </c>
       <c r="E140" s="3">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>448</v>
@@ -6155,7 +6155,7 @@
         <v>29</v>
       </c>
       <c r="E141">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F141" t="s">
         <v>451</v>
@@ -6175,7 +6175,7 @@
         <v>29</v>
       </c>
       <c r="E142" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>454</v>
@@ -6195,7 +6195,7 @@
         <v>29</v>
       </c>
       <c r="E143">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F143" t="s">
         <v>457</v>
@@ -6215,7 +6215,7 @@
         <v>29</v>
       </c>
       <c r="E144" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>460</v>
@@ -6235,7 +6235,7 @@
         <v>29</v>
       </c>
       <c r="E145">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F145" t="s">
         <v>463</v>
@@ -6255,7 +6255,7 @@
         <v>29</v>
       </c>
       <c r="E146" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>466</v>
@@ -6275,7 +6275,7 @@
         <v>29</v>
       </c>
       <c r="E147">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F147" t="s">
         <v>469</v>
@@ -6295,7 +6295,7 @@
         <v>29</v>
       </c>
       <c r="E148" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>472</v>
@@ -6315,7 +6315,7 @@
         <v>29</v>
       </c>
       <c r="E149">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="F149" t="s">
         <v>475</v>
@@ -6335,7 +6335,7 @@
         <v>29</v>
       </c>
       <c r="E150" s="3">
-        <v>24</v>
+        <v>11</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>478</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="E152" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>485</v>
@@ -6395,7 +6395,7 @@
         <v>29</v>
       </c>
       <c r="E153">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F153" t="s">
         <v>488</v>
@@ -6415,7 +6415,7 @@
         <v>29</v>
       </c>
       <c r="E154" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>491</v>
@@ -6435,7 +6435,7 @@
         <v>29</v>
       </c>
       <c r="E155">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F155" t="s">
         <v>494</v>
@@ -6455,7 +6455,7 @@
         <v>29</v>
       </c>
       <c r="E156" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>497</v>
@@ -6475,7 +6475,7 @@
         <v>29</v>
       </c>
       <c r="E157">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F157" t="s">
         <v>500</v>
@@ -6495,7 +6495,7 @@
         <v>29</v>
       </c>
       <c r="E158" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F158" s="3" t="s">
         <v>503</v>
@@ -6515,7 +6515,7 @@
         <v>29</v>
       </c>
       <c r="E159">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="F159" t="s">
         <v>506</v>
@@ -6535,7 +6535,7 @@
         <v>29</v>
       </c>
       <c r="E160" s="3">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>509</v>
@@ -6555,7 +6555,7 @@
         <v>29</v>
       </c>
       <c r="E161">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="F161" t="s">
         <v>512</v>
@@ -6575,7 +6575,7 @@
         <v>29</v>
       </c>
       <c r="E162" s="3">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>515</v>
@@ -6595,7 +6595,7 @@
         <v>29</v>
       </c>
       <c r="E163">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F163" t="s">
         <v>518</v>
@@ -6615,7 +6615,7 @@
         <v>29</v>
       </c>
       <c r="E164" s="3">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F164" s="3" t="s">
         <v>521</v>
@@ -6635,7 +6635,7 @@
         <v>29</v>
       </c>
       <c r="E165">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F165" t="s">
         <v>524</v>
@@ -6655,7 +6655,7 @@
         <v>29</v>
       </c>
       <c r="E166" s="3">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>527</v>
@@ -6675,7 +6675,7 @@
         <v>29</v>
       </c>
       <c r="E167">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F167" t="s">
         <v>530</v>
@@ -6695,7 +6695,7 @@
         <v>29</v>
       </c>
       <c r="E168" s="3">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>533</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="E169">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F169" t="s">
         <v>536</v>
@@ -6735,7 +6735,7 @@
         <v>29</v>
       </c>
       <c r="E170" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>539</v>
@@ -6755,7 +6755,7 @@
         <v>29</v>
       </c>
       <c r="E171">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F171" t="s">
         <v>542</v>
@@ -6775,7 +6775,7 @@
         <v>29</v>
       </c>
       <c r="E172" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>545</v>
@@ -6795,7 +6795,7 @@
         <v>29</v>
       </c>
       <c r="E173">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="F173" t="s">
         <v>548</v>
@@ -6815,7 +6815,7 @@
         <v>29</v>
       </c>
       <c r="E174" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>551</v>
@@ -6835,7 +6835,7 @@
         <v>29</v>
       </c>
       <c r="E175">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F175" t="s">
         <v>554</v>
@@ -6855,7 +6855,7 @@
         <v>29</v>
       </c>
       <c r="E176" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>557</v>
@@ -6875,7 +6875,7 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F177" t="s">
         <v>560</v>
@@ -6895,7 +6895,7 @@
         <v>29</v>
       </c>
       <c r="E178" s="3">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>563</v>
@@ -6915,7 +6915,7 @@
         <v>29</v>
       </c>
       <c r="E179">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F179" t="s">
         <v>566</v>
@@ -6935,7 +6935,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="3">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>569</v>
@@ -6955,7 +6955,7 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F181" t="s">
         <v>572</v>
@@ -6975,7 +6975,7 @@
         <v>29</v>
       </c>
       <c r="E182" s="3">
-        <v>15</v>
+        <v>6</v>
       </c>
       <c r="F182" s="3" t="s">
         <v>576</v>
@@ -6995,7 +6995,7 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F183" t="s">
         <v>579</v>
@@ -7035,7 +7035,7 @@
         <v>29</v>
       </c>
       <c r="E185">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F185" t="s">
         <v>585</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="E186" s="3">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>588</v>
@@ -7075,7 +7075,7 @@
         <v>29</v>
       </c>
       <c r="E187">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F187" t="s">
         <v>591</v>
@@ -7095,7 +7095,7 @@
         <v>29</v>
       </c>
       <c r="E188" s="3">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>594</v>
@@ -7115,7 +7115,7 @@
         <v>29</v>
       </c>
       <c r="E189">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="F189" t="s">
         <v>597</v>
@@ -7135,7 +7135,7 @@
         <v>29</v>
       </c>
       <c r="E190" s="3">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="F190" s="3" t="s">
         <v>600</v>
@@ -7155,7 +7155,7 @@
         <v>29</v>
       </c>
       <c r="E191">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F191" t="s">
         <v>603</v>
@@ -7175,7 +7175,7 @@
         <v>29</v>
       </c>
       <c r="E192" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>606</v>
@@ -7195,7 +7195,7 @@
         <v>29</v>
       </c>
       <c r="E193">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F193" t="s">
         <v>609</v>
@@ -7215,7 +7215,7 @@
         <v>29</v>
       </c>
       <c r="E194" s="3">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>612</v>
@@ -7235,7 +7235,7 @@
         <v>29</v>
       </c>
       <c r="E195">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F195" t="s">
         <v>615</v>
@@ -7255,7 +7255,7 @@
         <v>29</v>
       </c>
       <c r="E196" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>618</v>
@@ -7295,7 +7295,7 @@
         <v>29</v>
       </c>
       <c r="E198" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>624</v>
@@ -7315,7 +7315,7 @@
         <v>29</v>
       </c>
       <c r="E199">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F199" t="s">
         <v>627</v>
@@ -7335,7 +7335,7 @@
         <v>29</v>
       </c>
       <c r="E200" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F200" s="3" t="s">
         <v>630</v>
@@ -7355,7 +7355,7 @@
         <v>29</v>
       </c>
       <c r="E201">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="F201" t="s">
         <v>633</v>
@@ -7375,7 +7375,7 @@
         <v>29</v>
       </c>
       <c r="E202" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>636</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="E203">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F203" t="s">
         <v>639</v>
@@ -7415,7 +7415,7 @@
         <v>29</v>
       </c>
       <c r="E204" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>642</v>
@@ -7435,7 +7435,7 @@
         <v>29</v>
       </c>
       <c r="E205">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="F205" t="s">
         <v>645</v>
@@ -7455,7 +7455,7 @@
         <v>29</v>
       </c>
       <c r="E206" s="3">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>648</v>
@@ -7475,7 +7475,7 @@
         <v>29</v>
       </c>
       <c r="E207">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F207" t="s">
         <v>651</v>
@@ -7495,7 +7495,7 @@
         <v>29</v>
       </c>
       <c r="E208" s="3">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>654</v>
@@ -7515,7 +7515,7 @@
         <v>29</v>
       </c>
       <c r="E209">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F209" t="s">
         <v>657</v>
@@ -7535,7 +7535,7 @@
         <v>29</v>
       </c>
       <c r="E210" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>660</v>
@@ -7555,7 +7555,7 @@
         <v>29</v>
       </c>
       <c r="E211">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="F211" t="s">
         <v>663</v>
@@ -7575,7 +7575,7 @@
         <v>29</v>
       </c>
       <c r="E212" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>667</v>
@@ -7595,7 +7595,7 @@
         <v>29</v>
       </c>
       <c r="E213">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F213" t="s">
         <v>670</v>
@@ -7615,7 +7615,7 @@
         <v>29</v>
       </c>
       <c r="E214" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>673</v>
@@ -7635,7 +7635,7 @@
         <v>29</v>
       </c>
       <c r="E215">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F215" t="s">
         <v>676</v>
@@ -7655,7 +7655,7 @@
         <v>29</v>
       </c>
       <c r="E216" s="3">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>679</v>
@@ -7675,7 +7675,7 @@
         <v>29</v>
       </c>
       <c r="E217">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="F217" t="s">
         <v>682</v>
@@ -7695,7 +7695,7 @@
         <v>29</v>
       </c>
       <c r="E218" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>685</v>
@@ -7715,7 +7715,7 @@
         <v>29</v>
       </c>
       <c r="E219">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F219" t="s">
         <v>688</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="E220" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>691</v>
@@ -7755,7 +7755,7 @@
         <v>29</v>
       </c>
       <c r="E221">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F221" t="s">
         <v>694</v>
@@ -7775,7 +7775,7 @@
         <v>29</v>
       </c>
       <c r="E222" s="3">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F222" s="3" t="s">
         <v>697</v>
@@ -7795,7 +7795,7 @@
         <v>29</v>
       </c>
       <c r="E223">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F223" t="s">
         <v>700</v>
@@ -7815,7 +7815,7 @@
         <v>29</v>
       </c>
       <c r="E224" s="3">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>703</v>
@@ -7835,7 +7835,7 @@
         <v>29</v>
       </c>
       <c r="E225">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="F225" t="s">
         <v>706</v>
@@ -7855,7 +7855,7 @@
         <v>29</v>
       </c>
       <c r="E226" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>709</v>
@@ -7875,7 +7875,7 @@
         <v>29</v>
       </c>
       <c r="E227">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F227" t="s">
         <v>712</v>
@@ -7895,7 +7895,7 @@
         <v>29</v>
       </c>
       <c r="E228" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>715</v>
@@ -7915,7 +7915,7 @@
         <v>29</v>
       </c>
       <c r="E229">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F229" t="s">
         <v>718</v>
@@ -7935,7 +7935,7 @@
         <v>29</v>
       </c>
       <c r="E230" s="3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="F230" s="3" t="s">
         <v>721</v>
@@ -7955,7 +7955,7 @@
         <v>29</v>
       </c>
       <c r="E231">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F231" t="s">
         <v>724</v>
@@ -7975,7 +7975,7 @@
         <v>29</v>
       </c>
       <c r="E232" s="3">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>727</v>
@@ -7995,7 +7995,7 @@
         <v>29</v>
       </c>
       <c r="E233">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="F233" t="s">
         <v>730</v>
@@ -8015,7 +8015,7 @@
         <v>29</v>
       </c>
       <c r="E234" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>733</v>
@@ -8035,7 +8035,7 @@
         <v>29</v>
       </c>
       <c r="E235">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F235" t="s">
         <v>736</v>
@@ -8055,7 +8055,7 @@
         <v>29</v>
       </c>
       <c r="E236" s="3">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>739</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="E237">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F237" t="s">
         <v>742</v>
@@ -8095,7 +8095,7 @@
         <v>29</v>
       </c>
       <c r="E238" s="3">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>745</v>
@@ -8115,7 +8115,7 @@
         <v>29</v>
       </c>
       <c r="E239">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F239" t="s">
         <v>748</v>
@@ -8135,7 +8135,7 @@
         <v>29</v>
       </c>
       <c r="E240" s="3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>751</v>
@@ -8175,7 +8175,7 @@
         <v>29</v>
       </c>
       <c r="E242" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>758</v>
@@ -8195,7 +8195,7 @@
         <v>29</v>
       </c>
       <c r="E243">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F243" t="s">
         <v>761</v>
@@ -8215,7 +8215,7 @@
         <v>29</v>
       </c>
       <c r="E244" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>764</v>
@@ -8235,7 +8235,7 @@
         <v>29</v>
       </c>
       <c r="E245">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F245" t="s">
         <v>767</v>
@@ -8255,7 +8255,7 @@
         <v>29</v>
       </c>
       <c r="E246" s="3">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>770</v>
@@ -8275,7 +8275,7 @@
         <v>29</v>
       </c>
       <c r="E247">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F247" t="s">
         <v>773</v>
@@ -8295,7 +8295,7 @@
         <v>29</v>
       </c>
       <c r="E248" s="3">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>776</v>
@@ -8315,7 +8315,7 @@
         <v>29</v>
       </c>
       <c r="E249">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F249" t="s">
         <v>779</v>
@@ -8335,7 +8335,7 @@
         <v>29</v>
       </c>
       <c r="E250" s="3">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>782</v>
@@ -8375,7 +8375,7 @@
         <v>29</v>
       </c>
       <c r="E252" s="3">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>788</v>
@@ -8395,7 +8395,7 @@
         <v>29</v>
       </c>
       <c r="E253">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F253" t="s">
         <v>791</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="E254" s="3">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>794</v>
@@ -8435,7 +8435,7 @@
         <v>29</v>
       </c>
       <c r="E255">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="F255" t="s">
         <v>797</v>
@@ -8475,7 +8475,7 @@
         <v>29</v>
       </c>
       <c r="E257">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F257" t="s">
         <v>803</v>
@@ -8495,7 +8495,7 @@
         <v>29</v>
       </c>
       <c r="E258" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>806</v>
@@ -8515,7 +8515,7 @@
         <v>29</v>
       </c>
       <c r="E259">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="F259" t="s">
         <v>809</v>
@@ -8535,7 +8535,7 @@
         <v>29</v>
       </c>
       <c r="E260" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>812</v>
@@ -8555,7 +8555,7 @@
         <v>29</v>
       </c>
       <c r="E261">
-        <v>23</v>
+        <v>14</v>
       </c>
       <c r="F261" t="s">
         <v>815</v>
@@ -8575,7 +8575,7 @@
         <v>29</v>
       </c>
       <c r="E262" s="3">
-        <v>11</v>
+        <v>20</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>818</v>
@@ -8595,7 +8595,7 @@
         <v>29</v>
       </c>
       <c r="E263">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F263" t="s">
         <v>821</v>
@@ -8615,7 +8615,7 @@
         <v>29</v>
       </c>
       <c r="E264" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>824</v>
@@ -8655,7 +8655,7 @@
         <v>29</v>
       </c>
       <c r="E266" s="3">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F266" s="3" t="s">
         <v>830</v>
@@ -8675,7 +8675,7 @@
         <v>29</v>
       </c>
       <c r="E267">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F267" t="s">
         <v>833</v>
@@ -8695,7 +8695,7 @@
         <v>29</v>
       </c>
       <c r="E268" s="3">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>836</v>
@@ -8735,7 +8735,7 @@
         <v>29</v>
       </c>
       <c r="E270" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>842</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="E271">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F271" t="s">
         <v>845</v>
@@ -8775,7 +8775,7 @@
         <v>29</v>
       </c>
       <c r="E272" s="3">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>849</v>
@@ -8795,7 +8795,7 @@
         <v>29</v>
       </c>
       <c r="E273">
-        <v>24</v>
+        <v>5</v>
       </c>
       <c r="F273" t="s">
         <v>852</v>
@@ -8815,7 +8815,7 @@
         <v>29</v>
       </c>
       <c r="E274" s="3">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>855</v>
@@ -8835,7 +8835,7 @@
         <v>29</v>
       </c>
       <c r="E275">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F275" t="s">
         <v>858</v>
@@ -8855,7 +8855,7 @@
         <v>29</v>
       </c>
       <c r="E276" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>861</v>
@@ -8875,7 +8875,7 @@
         <v>29</v>
       </c>
       <c r="E277">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F277" t="s">
         <v>864</v>
@@ -8895,7 +8895,7 @@
         <v>29</v>
       </c>
       <c r="E278" s="3">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>867</v>
@@ -8915,7 +8915,7 @@
         <v>29</v>
       </c>
       <c r="E279">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F279" t="s">
         <v>870</v>
@@ -8935,7 +8935,7 @@
         <v>29</v>
       </c>
       <c r="E280" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>873</v>
@@ -8955,7 +8955,7 @@
         <v>29</v>
       </c>
       <c r="E281">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F281" t="s">
         <v>876</v>
@@ -8975,7 +8975,7 @@
         <v>29</v>
       </c>
       <c r="E282" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>879</v>
@@ -8995,7 +8995,7 @@
         <v>29</v>
       </c>
       <c r="E283">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="F283" t="s">
         <v>882</v>
@@ -9015,7 +9015,7 @@
         <v>29</v>
       </c>
       <c r="E284" s="3">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>885</v>
@@ -9035,7 +9035,7 @@
         <v>29</v>
       </c>
       <c r="E285">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="F285" t="s">
         <v>888</v>
@@ -9055,7 +9055,7 @@
         <v>29</v>
       </c>
       <c r="E286" s="3">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>891</v>
@@ -9075,7 +9075,7 @@
         <v>29</v>
       </c>
       <c r="E287">
-        <v>7</v>
+        <v>18</v>
       </c>
       <c r="F287" t="s">
         <v>894</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="E288" s="3">
-        <v>23</v>
+        <v>9</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>897</v>
@@ -9115,7 +9115,7 @@
         <v>29</v>
       </c>
       <c r="E289">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F289" t="s">
         <v>900</v>
@@ -9135,7 +9135,7 @@
         <v>29</v>
       </c>
       <c r="E290" s="3">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>903</v>
@@ -9155,7 +9155,7 @@
         <v>29</v>
       </c>
       <c r="E291">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="F291" t="s">
         <v>906</v>
@@ -9175,7 +9175,7 @@
         <v>29</v>
       </c>
       <c r="E292" s="3">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>909</v>
@@ -9195,7 +9195,7 @@
         <v>29</v>
       </c>
       <c r="E293">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="F293" t="s">
         <v>912</v>
@@ -9215,7 +9215,7 @@
         <v>29</v>
       </c>
       <c r="E294" s="3">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>915</v>
@@ -9235,7 +9235,7 @@
         <v>29</v>
       </c>
       <c r="E295">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="F295" t="s">
         <v>918</v>
@@ -9255,7 +9255,7 @@
         <v>29</v>
       </c>
       <c r="E296" s="3">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="F296" s="3" t="s">
         <v>921</v>
@@ -9275,7 +9275,7 @@
         <v>29</v>
       </c>
       <c r="E297">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F297" t="s">
         <v>924</v>
@@ -9295,7 +9295,7 @@
         <v>29</v>
       </c>
       <c r="E298" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>927</v>
@@ -9315,7 +9315,7 @@
         <v>29</v>
       </c>
       <c r="E299">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F299" t="s">
         <v>930</v>
@@ -9335,7 +9335,7 @@
         <v>29</v>
       </c>
       <c r="E300" s="3">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F300" s="3" t="s">
         <v>933</v>
@@ -9355,7 +9355,7 @@
         <v>29</v>
       </c>
       <c r="E301">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F301" t="s">
         <v>936</v>

--- a/load-report.xlsx
+++ b/load-report.xlsx
@@ -59,7 +59,7 @@
     <t>Total Execution Duration</t>
   </si>
   <si>
-    <t>4.30s</t>
+    <t>4.60s</t>
   </si>
   <si>
     <t>Fast Execution</t>
@@ -68,7 +68,7 @@
     <t>Average Case Speed</t>
   </si>
   <si>
-    <t>14.3ms</t>
+    <t>15.3ms</t>
   </si>
   <si>
     <t>Optimal Pacing</t>
@@ -104,7 +104,7 @@
     <t>PASS</t>
   </si>
   <si>
-    <t>2026-08-27 02:59:33</t>
+    <t>2026-08-27 03:06:09</t>
   </si>
   <si>
     <t>PERF_LOD_002</t>
@@ -113,7 +113,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 02:59:43</t>
+    <t>2026-08-27 03:06:19</t>
   </si>
   <si>
     <t>PERF_LOD_003</t>
@@ -122,7 +122,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 02:59:53</t>
+    <t>2026-08-27 03:06:29</t>
   </si>
   <si>
     <t>PERF_LOD_004</t>
@@ -131,7 +131,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:03</t>
+    <t>2026-08-27 03:06:39</t>
   </si>
   <si>
     <t>PERF_LOD_005</t>
@@ -140,7 +140,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:13</t>
+    <t>2026-08-27 03:06:49</t>
   </si>
   <si>
     <t>PERF_LOD_006</t>
@@ -149,7 +149,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:23</t>
+    <t>2026-08-27 03:06:59</t>
   </si>
   <si>
     <t>PERF_LOD_007</t>
@@ -158,7 +158,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:33</t>
+    <t>2026-08-27 03:07:09</t>
   </si>
   <si>
     <t>PERF_LOD_008</t>
@@ -167,7 +167,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:43</t>
+    <t>2026-08-27 03:07:19</t>
   </si>
   <si>
     <t>PERF_LOD_009</t>
@@ -176,7 +176,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:00:53</t>
+    <t>2026-08-27 03:07:29</t>
   </si>
   <si>
     <t>PERF_LOD_010</t>
@@ -185,7 +185,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:03</t>
+    <t>2026-08-27 03:07:39</t>
   </si>
   <si>
     <t>PERF_LOD_011</t>
@@ -194,7 +194,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:13</t>
+    <t>2026-08-27 03:07:49</t>
   </si>
   <si>
     <t>PERF_LOD_012</t>
@@ -203,7 +203,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:23</t>
+    <t>2026-08-27 03:07:59</t>
   </si>
   <si>
     <t>PERF_LOD_013</t>
@@ -212,7 +212,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:33</t>
+    <t>2026-08-27 03:08:09</t>
   </si>
   <si>
     <t>PERF_LOD_014</t>
@@ -221,7 +221,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:43</t>
+    <t>2026-08-27 03:08:19</t>
   </si>
   <si>
     <t>PERF_LOD_015</t>
@@ -230,7 +230,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:01:53</t>
+    <t>2026-08-27 03:08:29</t>
   </si>
   <si>
     <t>PERF_LOD_016</t>
@@ -239,7 +239,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:03</t>
+    <t>2026-08-27 03:08:39</t>
   </si>
   <si>
     <t>PERF_LOD_017</t>
@@ -248,7 +248,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:13</t>
+    <t>2026-08-27 03:08:49</t>
   </si>
   <si>
     <t>PERF_LOD_018</t>
@@ -257,7 +257,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:23</t>
+    <t>2026-08-27 03:08:59</t>
   </si>
   <si>
     <t>PERF_LOD_019</t>
@@ -266,7 +266,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:33</t>
+    <t>2026-08-27 03:09:09</t>
   </si>
   <si>
     <t>PERF_LOD_020</t>
@@ -275,7 +275,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:43</t>
+    <t>2026-08-27 03:09:19</t>
   </si>
   <si>
     <t>PERF_LOD_021</t>
@@ -284,7 +284,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:02:53</t>
+    <t>2026-08-27 03:09:29</t>
   </si>
   <si>
     <t>PERF_LOD_022</t>
@@ -293,7 +293,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:03</t>
+    <t>2026-08-27 03:09:39</t>
   </si>
   <si>
     <t>PERF_LOD_023</t>
@@ -302,7 +302,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:13</t>
+    <t>2026-08-27 03:09:49</t>
   </si>
   <si>
     <t>PERF_LOD_024</t>
@@ -311,7 +311,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:23</t>
+    <t>2026-08-27 03:09:59</t>
   </si>
   <si>
     <t>PERF_LOD_025</t>
@@ -320,7 +320,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:33</t>
+    <t>2026-08-27 03:10:09</t>
   </si>
   <si>
     <t>PERF_LOD_026</t>
@@ -329,7 +329,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:43</t>
+    <t>2026-08-27 03:10:19</t>
   </si>
   <si>
     <t>PERF_LOD_027</t>
@@ -338,7 +338,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:03:53</t>
+    <t>2026-08-27 03:10:29</t>
   </si>
   <si>
     <t>PERF_LOD_028</t>
@@ -347,7 +347,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:03</t>
+    <t>2026-08-27 03:10:39</t>
   </si>
   <si>
     <t>PERF_LOD_029</t>
@@ -356,7 +356,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:13</t>
+    <t>2026-08-27 03:10:49</t>
   </si>
   <si>
     <t>PERF_LOD_030</t>
@@ -365,7 +365,7 @@
     <t>Verify correct behavior of Concurrent User Simulation - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:23</t>
+    <t>2026-08-27 03:10:59</t>
   </si>
   <si>
     <t>PERF_LOD_031</t>
@@ -377,7 +377,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:33</t>
+    <t>2026-08-27 03:11:09</t>
   </si>
   <si>
     <t>PERF_LOD_032</t>
@@ -386,7 +386,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:43</t>
+    <t>2026-08-27 03:11:19</t>
   </si>
   <si>
     <t>PERF_LOD_033</t>
@@ -395,7 +395,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:04:53</t>
+    <t>2026-08-27 03:11:29</t>
   </si>
   <si>
     <t>PERF_LOD_034</t>
@@ -404,7 +404,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:03</t>
+    <t>2026-08-27 03:11:39</t>
   </si>
   <si>
     <t>PERF_LOD_035</t>
@@ -413,7 +413,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:13</t>
+    <t>2026-08-27 03:11:49</t>
   </si>
   <si>
     <t>PERF_LOD_036</t>
@@ -422,7 +422,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:23</t>
+    <t>2026-08-27 03:11:59</t>
   </si>
   <si>
     <t>PERF_LOD_037</t>
@@ -431,7 +431,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:33</t>
+    <t>2026-08-27 03:12:09</t>
   </si>
   <si>
     <t>PERF_LOD_038</t>
@@ -440,7 +440,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:43</t>
+    <t>2026-08-27 03:12:19</t>
   </si>
   <si>
     <t>PERF_LOD_039</t>
@@ -449,7 +449,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:05:53</t>
+    <t>2026-08-27 03:12:29</t>
   </si>
   <si>
     <t>PERF_LOD_040</t>
@@ -458,7 +458,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:03</t>
+    <t>2026-08-27 03:12:39</t>
   </si>
   <si>
     <t>PERF_LOD_041</t>
@@ -467,7 +467,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:13</t>
+    <t>2026-08-27 03:12:49</t>
   </si>
   <si>
     <t>PERF_LOD_042</t>
@@ -476,7 +476,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:23</t>
+    <t>2026-08-27 03:12:59</t>
   </si>
   <si>
     <t>PERF_LOD_043</t>
@@ -485,7 +485,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:33</t>
+    <t>2026-08-27 03:13:09</t>
   </si>
   <si>
     <t>PERF_LOD_044</t>
@@ -494,7 +494,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:43</t>
+    <t>2026-08-27 03:13:19</t>
   </si>
   <si>
     <t>PERF_LOD_045</t>
@@ -503,7 +503,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:06:53</t>
+    <t>2026-08-27 03:13:29</t>
   </si>
   <si>
     <t>PERF_LOD_046</t>
@@ -512,7 +512,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:03</t>
+    <t>2026-08-27 03:13:39</t>
   </si>
   <si>
     <t>PERF_LOD_047</t>
@@ -521,7 +521,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:13</t>
+    <t>2026-08-27 03:13:49</t>
   </si>
   <si>
     <t>PERF_LOD_048</t>
@@ -530,7 +530,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:23</t>
+    <t>2026-08-27 03:13:59</t>
   </si>
   <si>
     <t>PERF_LOD_049</t>
@@ -539,7 +539,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:33</t>
+    <t>2026-08-27 03:14:09</t>
   </si>
   <si>
     <t>PERF_LOD_050</t>
@@ -548,7 +548,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:43</t>
+    <t>2026-08-27 03:14:19</t>
   </si>
   <si>
     <t>PERF_LOD_051</t>
@@ -557,7 +557,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:07:53</t>
+    <t>2026-08-27 03:14:29</t>
   </si>
   <si>
     <t>PERF_LOD_052</t>
@@ -566,7 +566,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:03</t>
+    <t>2026-08-27 03:14:39</t>
   </si>
   <si>
     <t>PERF_LOD_053</t>
@@ -575,7 +575,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:13</t>
+    <t>2026-08-27 03:14:49</t>
   </si>
   <si>
     <t>PERF_LOD_054</t>
@@ -584,7 +584,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:23</t>
+    <t>2026-08-27 03:14:59</t>
   </si>
   <si>
     <t>PERF_LOD_055</t>
@@ -593,7 +593,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:33</t>
+    <t>2026-08-27 03:15:09</t>
   </si>
   <si>
     <t>PERF_LOD_056</t>
@@ -602,7 +602,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:43</t>
+    <t>2026-08-27 03:15:19</t>
   </si>
   <si>
     <t>PERF_LOD_057</t>
@@ -611,7 +611,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:08:53</t>
+    <t>2026-08-27 03:15:29</t>
   </si>
   <si>
     <t>PERF_LOD_058</t>
@@ -620,7 +620,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:03</t>
+    <t>2026-08-27 03:15:39</t>
   </si>
   <si>
     <t>PERF_LOD_059</t>
@@ -629,7 +629,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:13</t>
+    <t>2026-08-27 03:15:49</t>
   </si>
   <si>
     <t>PERF_LOD_060</t>
@@ -638,7 +638,7 @@
     <t>Verify correct behavior of Endpoint Latency - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:23</t>
+    <t>2026-08-27 03:15:59</t>
   </si>
   <si>
     <t>PERF_LOD_061</t>
@@ -650,7 +650,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:33</t>
+    <t>2026-08-27 03:16:09</t>
   </si>
   <si>
     <t>PERF_LOD_062</t>
@@ -659,7 +659,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:43</t>
+    <t>2026-08-27 03:16:19</t>
   </si>
   <si>
     <t>PERF_LOD_063</t>
@@ -668,7 +668,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:09:53</t>
+    <t>2026-08-27 03:16:29</t>
   </si>
   <si>
     <t>PERF_LOD_064</t>
@@ -677,7 +677,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:03</t>
+    <t>2026-08-27 03:16:39</t>
   </si>
   <si>
     <t>PERF_LOD_065</t>
@@ -686,7 +686,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:13</t>
+    <t>2026-08-27 03:16:49</t>
   </si>
   <si>
     <t>PERF_LOD_066</t>
@@ -695,7 +695,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:23</t>
+    <t>2026-08-27 03:16:59</t>
   </si>
   <si>
     <t>PERF_LOD_067</t>
@@ -704,7 +704,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:33</t>
+    <t>2026-08-27 03:17:09</t>
   </si>
   <si>
     <t>PERF_LOD_068</t>
@@ -713,7 +713,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:43</t>
+    <t>2026-08-27 03:17:19</t>
   </si>
   <si>
     <t>PERF_LOD_069</t>
@@ -722,7 +722,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:10:53</t>
+    <t>2026-08-27 03:17:29</t>
   </si>
   <si>
     <t>PERF_LOD_070</t>
@@ -731,7 +731,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:03</t>
+    <t>2026-08-27 03:17:39</t>
   </si>
   <si>
     <t>PERF_LOD_071</t>
@@ -740,7 +740,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:13</t>
+    <t>2026-08-27 03:17:49</t>
   </si>
   <si>
     <t>PERF_LOD_072</t>
@@ -749,7 +749,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:23</t>
+    <t>2026-08-27 03:17:59</t>
   </si>
   <si>
     <t>PERF_LOD_073</t>
@@ -758,7 +758,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:33</t>
+    <t>2026-08-27 03:18:09</t>
   </si>
   <si>
     <t>PERF_LOD_074</t>
@@ -767,7 +767,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:43</t>
+    <t>2026-08-27 03:18:19</t>
   </si>
   <si>
     <t>PERF_LOD_075</t>
@@ -776,7 +776,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:11:53</t>
+    <t>2026-08-27 03:18:29</t>
   </si>
   <si>
     <t>PERF_LOD_076</t>
@@ -785,7 +785,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:03</t>
+    <t>2026-08-27 03:18:39</t>
   </si>
   <si>
     <t>PERF_LOD_077</t>
@@ -794,7 +794,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:13</t>
+    <t>2026-08-27 03:18:49</t>
   </si>
   <si>
     <t>PERF_LOD_078</t>
@@ -803,7 +803,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:23</t>
+    <t>2026-08-27 03:18:59</t>
   </si>
   <si>
     <t>PERF_LOD_079</t>
@@ -812,7 +812,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:33</t>
+    <t>2026-08-27 03:19:09</t>
   </si>
   <si>
     <t>PERF_LOD_080</t>
@@ -821,7 +821,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:43</t>
+    <t>2026-08-27 03:19:19</t>
   </si>
   <si>
     <t>PERF_LOD_081</t>
@@ -830,7 +830,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:12:53</t>
+    <t>2026-08-27 03:19:29</t>
   </si>
   <si>
     <t>PERF_LOD_082</t>
@@ -839,7 +839,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:03</t>
+    <t>2026-08-27 03:19:39</t>
   </si>
   <si>
     <t>PERF_LOD_083</t>
@@ -848,7 +848,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:13</t>
+    <t>2026-08-27 03:19:49</t>
   </si>
   <si>
     <t>PERF_LOD_084</t>
@@ -857,7 +857,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:23</t>
+    <t>2026-08-27 03:19:59</t>
   </si>
   <si>
     <t>PERF_LOD_085</t>
@@ -866,7 +866,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:33</t>
+    <t>2026-08-27 03:20:09</t>
   </si>
   <si>
     <t>PERF_LOD_086</t>
@@ -875,7 +875,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:43</t>
+    <t>2026-08-27 03:20:19</t>
   </si>
   <si>
     <t>PERF_LOD_087</t>
@@ -884,7 +884,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:13:53</t>
+    <t>2026-08-27 03:20:29</t>
   </si>
   <si>
     <t>PERF_LOD_088</t>
@@ -893,7 +893,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:03</t>
+    <t>2026-08-27 03:20:39</t>
   </si>
   <si>
     <t>PERF_LOD_089</t>
@@ -902,7 +902,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:13</t>
+    <t>2026-08-27 03:20:49</t>
   </si>
   <si>
     <t>PERF_LOD_090</t>
@@ -911,7 +911,7 @@
     <t>Verify correct behavior of Throughput Pacing - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:23</t>
+    <t>2026-08-27 03:20:59</t>
   </si>
   <si>
     <t>PERF_LOD_091</t>
@@ -923,7 +923,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:33</t>
+    <t>2026-08-27 03:21:09</t>
   </si>
   <si>
     <t>PERF_LOD_092</t>
@@ -932,7 +932,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:43</t>
+    <t>2026-08-27 03:21:19</t>
   </si>
   <si>
     <t>PERF_LOD_093</t>
@@ -941,7 +941,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:14:53</t>
+    <t>2026-08-27 03:21:29</t>
   </si>
   <si>
     <t>PERF_LOD_094</t>
@@ -950,7 +950,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:03</t>
+    <t>2026-08-27 03:21:39</t>
   </si>
   <si>
     <t>PERF_LOD_095</t>
@@ -959,7 +959,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:13</t>
+    <t>2026-08-27 03:21:49</t>
   </si>
   <si>
     <t>PERF_LOD_096</t>
@@ -968,7 +968,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:23</t>
+    <t>2026-08-27 03:21:59</t>
   </si>
   <si>
     <t>PERF_LOD_097</t>
@@ -977,7 +977,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:33</t>
+    <t>2026-08-27 03:22:09</t>
   </si>
   <si>
     <t>PERF_LOD_098</t>
@@ -986,7 +986,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:43</t>
+    <t>2026-08-27 03:22:19</t>
   </si>
   <si>
     <t>PERF_LOD_099</t>
@@ -995,7 +995,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:15:53</t>
+    <t>2026-08-27 03:22:29</t>
   </si>
   <si>
     <t>PERF_LOD_100</t>
@@ -1004,7 +1004,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:03</t>
+    <t>2026-08-27 03:22:39</t>
   </si>
   <si>
     <t>PERF_LOD_101</t>
@@ -1013,7 +1013,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:13</t>
+    <t>2026-08-27 03:22:49</t>
   </si>
   <si>
     <t>PERF_LOD_102</t>
@@ -1022,7 +1022,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:23</t>
+    <t>2026-08-27 03:22:59</t>
   </si>
   <si>
     <t>PERF_LOD_103</t>
@@ -1031,7 +1031,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:33</t>
+    <t>2026-08-27 03:23:09</t>
   </si>
   <si>
     <t>PERF_LOD_104</t>
@@ -1040,7 +1040,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:43</t>
+    <t>2026-08-27 03:23:19</t>
   </si>
   <si>
     <t>PERF_LOD_105</t>
@@ -1049,7 +1049,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:16:53</t>
+    <t>2026-08-27 03:23:29</t>
   </si>
   <si>
     <t>PERF_LOD_106</t>
@@ -1058,7 +1058,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:03</t>
+    <t>2026-08-27 03:23:39</t>
   </si>
   <si>
     <t>PERF_LOD_107</t>
@@ -1067,7 +1067,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:13</t>
+    <t>2026-08-27 03:23:49</t>
   </si>
   <si>
     <t>PERF_LOD_108</t>
@@ -1076,7 +1076,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:23</t>
+    <t>2026-08-27 03:23:59</t>
   </si>
   <si>
     <t>PERF_LOD_109</t>
@@ -1085,7 +1085,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:33</t>
+    <t>2026-08-27 03:24:09</t>
   </si>
   <si>
     <t>PERF_LOD_110</t>
@@ -1094,7 +1094,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:43</t>
+    <t>2026-08-27 03:24:19</t>
   </si>
   <si>
     <t>PERF_LOD_111</t>
@@ -1103,7 +1103,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:17:53</t>
+    <t>2026-08-27 03:24:29</t>
   </si>
   <si>
     <t>PERF_LOD_112</t>
@@ -1112,7 +1112,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:03</t>
+    <t>2026-08-27 03:24:39</t>
   </si>
   <si>
     <t>PERF_LOD_113</t>
@@ -1121,7 +1121,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:13</t>
+    <t>2026-08-27 03:24:49</t>
   </si>
   <si>
     <t>PERF_LOD_114</t>
@@ -1130,7 +1130,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:23</t>
+    <t>2026-08-27 03:24:59</t>
   </si>
   <si>
     <t>PERF_LOD_115</t>
@@ -1139,7 +1139,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:33</t>
+    <t>2026-08-27 03:25:09</t>
   </si>
   <si>
     <t>PERF_LOD_116</t>
@@ -1148,7 +1148,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:43</t>
+    <t>2026-08-27 03:25:19</t>
   </si>
   <si>
     <t>PERF_LOD_117</t>
@@ -1157,7 +1157,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:18:53</t>
+    <t>2026-08-27 03:25:29</t>
   </si>
   <si>
     <t>PERF_LOD_118</t>
@@ -1166,7 +1166,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:03</t>
+    <t>2026-08-27 03:25:39</t>
   </si>
   <si>
     <t>PERF_LOD_119</t>
@@ -1175,7 +1175,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:13</t>
+    <t>2026-08-27 03:25:49</t>
   </si>
   <si>
     <t>PERF_LOD_120</t>
@@ -1184,7 +1184,7 @@
     <t>Verify correct behavior of Database Connection Pool - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:23</t>
+    <t>2026-08-27 03:25:59</t>
   </si>
   <si>
     <t>PERF_LOD_121</t>
@@ -1196,7 +1196,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:33</t>
+    <t>2026-08-27 03:26:09</t>
   </si>
   <si>
     <t>PERF_LOD_122</t>
@@ -1205,7 +1205,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:43</t>
+    <t>2026-08-27 03:26:19</t>
   </si>
   <si>
     <t>PERF_LOD_123</t>
@@ -1214,7 +1214,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:19:53</t>
+    <t>2026-08-27 03:26:29</t>
   </si>
   <si>
     <t>PERF_LOD_124</t>
@@ -1223,7 +1223,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:03</t>
+    <t>2026-08-27 03:26:39</t>
   </si>
   <si>
     <t>PERF_LOD_125</t>
@@ -1232,7 +1232,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:13</t>
+    <t>2026-08-27 03:26:49</t>
   </si>
   <si>
     <t>PERF_LOD_126</t>
@@ -1241,7 +1241,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:23</t>
+    <t>2026-08-27 03:26:59</t>
   </si>
   <si>
     <t>PERF_LOD_127</t>
@@ -1250,7 +1250,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:33</t>
+    <t>2026-08-27 03:27:09</t>
   </si>
   <si>
     <t>PERF_LOD_128</t>
@@ -1259,7 +1259,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:43</t>
+    <t>2026-08-27 03:27:19</t>
   </si>
   <si>
     <t>PERF_LOD_129</t>
@@ -1268,7 +1268,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:20:53</t>
+    <t>2026-08-27 03:27:29</t>
   </si>
   <si>
     <t>PERF_LOD_130</t>
@@ -1277,7 +1277,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:03</t>
+    <t>2026-08-27 03:27:39</t>
   </si>
   <si>
     <t>PERF_LOD_131</t>
@@ -1286,7 +1286,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:13</t>
+    <t>2026-08-27 03:27:49</t>
   </si>
   <si>
     <t>PERF_LOD_132</t>
@@ -1295,7 +1295,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:23</t>
+    <t>2026-08-27 03:27:59</t>
   </si>
   <si>
     <t>PERF_LOD_133</t>
@@ -1304,7 +1304,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:33</t>
+    <t>2026-08-27 03:28:09</t>
   </si>
   <si>
     <t>PERF_LOD_134</t>
@@ -1313,7 +1313,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:43</t>
+    <t>2026-08-27 03:28:19</t>
   </si>
   <si>
     <t>PERF_LOD_135</t>
@@ -1322,7 +1322,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:21:53</t>
+    <t>2026-08-27 03:28:29</t>
   </si>
   <si>
     <t>PERF_LOD_136</t>
@@ -1331,7 +1331,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:03</t>
+    <t>2026-08-27 03:28:39</t>
   </si>
   <si>
     <t>PERF_LOD_137</t>
@@ -1340,7 +1340,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:13</t>
+    <t>2026-08-27 03:28:49</t>
   </si>
   <si>
     <t>PERF_LOD_138</t>
@@ -1349,7 +1349,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:23</t>
+    <t>2026-08-27 03:28:59</t>
   </si>
   <si>
     <t>PERF_LOD_139</t>
@@ -1358,7 +1358,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:33</t>
+    <t>2026-08-27 03:29:09</t>
   </si>
   <si>
     <t>PERF_LOD_140</t>
@@ -1367,7 +1367,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:43</t>
+    <t>2026-08-27 03:29:19</t>
   </si>
   <si>
     <t>PERF_LOD_141</t>
@@ -1376,7 +1376,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:22:53</t>
+    <t>2026-08-27 03:29:29</t>
   </si>
   <si>
     <t>PERF_LOD_142</t>
@@ -1385,7 +1385,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:03</t>
+    <t>2026-08-27 03:29:39</t>
   </si>
   <si>
     <t>PERF_LOD_143</t>
@@ -1394,7 +1394,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:13</t>
+    <t>2026-08-27 03:29:49</t>
   </si>
   <si>
     <t>PERF_LOD_144</t>
@@ -1403,7 +1403,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:23</t>
+    <t>2026-08-27 03:29:59</t>
   </si>
   <si>
     <t>PERF_LOD_145</t>
@@ -1412,7 +1412,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:33</t>
+    <t>2026-08-27 03:30:09</t>
   </si>
   <si>
     <t>PERF_LOD_146</t>
@@ -1421,7 +1421,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:43</t>
+    <t>2026-08-27 03:30:19</t>
   </si>
   <si>
     <t>PERF_LOD_147</t>
@@ -1430,7 +1430,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:23:53</t>
+    <t>2026-08-27 03:30:29</t>
   </si>
   <si>
     <t>PERF_LOD_148</t>
@@ -1439,7 +1439,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:03</t>
+    <t>2026-08-27 03:30:39</t>
   </si>
   <si>
     <t>PERF_LOD_149</t>
@@ -1448,7 +1448,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:13</t>
+    <t>2026-08-27 03:30:49</t>
   </si>
   <si>
     <t>PERF_LOD_150</t>
@@ -1457,7 +1457,7 @@
     <t>Verify correct behavior of Memory Leak Audit - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:23</t>
+    <t>2026-08-27 03:30:59</t>
   </si>
   <si>
     <t>PERF_LOD_151</t>
@@ -1469,7 +1469,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:33</t>
+    <t>2026-08-27 03:31:09</t>
   </si>
   <si>
     <t>PERF_LOD_152</t>
@@ -1478,7 +1478,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:43</t>
+    <t>2026-08-27 03:31:19</t>
   </si>
   <si>
     <t>PERF_LOD_153</t>
@@ -1487,7 +1487,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:24:53</t>
+    <t>2026-08-27 03:31:29</t>
   </si>
   <si>
     <t>PERF_LOD_154</t>
@@ -1496,7 +1496,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:03</t>
+    <t>2026-08-27 03:31:39</t>
   </si>
   <si>
     <t>PERF_LOD_155</t>
@@ -1505,7 +1505,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:13</t>
+    <t>2026-08-27 03:31:49</t>
   </si>
   <si>
     <t>PERF_LOD_156</t>
@@ -1514,7 +1514,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:23</t>
+    <t>2026-08-27 03:31:59</t>
   </si>
   <si>
     <t>PERF_LOD_157</t>
@@ -1523,7 +1523,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:33</t>
+    <t>2026-08-27 03:32:09</t>
   </si>
   <si>
     <t>PERF_LOD_158</t>
@@ -1532,7 +1532,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:43</t>
+    <t>2026-08-27 03:32:19</t>
   </si>
   <si>
     <t>PERF_LOD_159</t>
@@ -1541,7 +1541,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:25:53</t>
+    <t>2026-08-27 03:32:29</t>
   </si>
   <si>
     <t>PERF_LOD_160</t>
@@ -1550,7 +1550,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:03</t>
+    <t>2026-08-27 03:32:39</t>
   </si>
   <si>
     <t>PERF_LOD_161</t>
@@ -1559,7 +1559,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:13</t>
+    <t>2026-08-27 03:32:49</t>
   </si>
   <si>
     <t>PERF_LOD_162</t>
@@ -1568,7 +1568,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:23</t>
+    <t>2026-08-27 03:32:59</t>
   </si>
   <si>
     <t>PERF_LOD_163</t>
@@ -1577,7 +1577,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:33</t>
+    <t>2026-08-27 03:33:09</t>
   </si>
   <si>
     <t>PERF_LOD_164</t>
@@ -1586,7 +1586,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:43</t>
+    <t>2026-08-27 03:33:19</t>
   </si>
   <si>
     <t>PERF_LOD_165</t>
@@ -1595,7 +1595,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:26:53</t>
+    <t>2026-08-27 03:33:29</t>
   </si>
   <si>
     <t>PERF_LOD_166</t>
@@ -1604,7 +1604,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:03</t>
+    <t>2026-08-27 03:33:39</t>
   </si>
   <si>
     <t>PERF_LOD_167</t>
@@ -1613,7 +1613,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:13</t>
+    <t>2026-08-27 03:33:49</t>
   </si>
   <si>
     <t>PERF_LOD_168</t>
@@ -1622,7 +1622,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:23</t>
+    <t>2026-08-27 03:33:59</t>
   </si>
   <si>
     <t>PERF_LOD_169</t>
@@ -1631,7 +1631,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:33</t>
+    <t>2026-08-27 03:34:09</t>
   </si>
   <si>
     <t>PERF_LOD_170</t>
@@ -1640,7 +1640,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:43</t>
+    <t>2026-08-27 03:34:19</t>
   </si>
   <si>
     <t>PERF_LOD_171</t>
@@ -1649,7 +1649,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:27:53</t>
+    <t>2026-08-27 03:34:29</t>
   </si>
   <si>
     <t>PERF_LOD_172</t>
@@ -1658,7 +1658,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:03</t>
+    <t>2026-08-27 03:34:39</t>
   </si>
   <si>
     <t>PERF_LOD_173</t>
@@ -1667,7 +1667,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:13</t>
+    <t>2026-08-27 03:34:49</t>
   </si>
   <si>
     <t>PERF_LOD_174</t>
@@ -1676,7 +1676,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:23</t>
+    <t>2026-08-27 03:34:59</t>
   </si>
   <si>
     <t>PERF_LOD_175</t>
@@ -1685,7 +1685,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:33</t>
+    <t>2026-08-27 03:35:09</t>
   </si>
   <si>
     <t>PERF_LOD_176</t>
@@ -1694,7 +1694,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:43</t>
+    <t>2026-08-27 03:35:19</t>
   </si>
   <si>
     <t>PERF_LOD_177</t>
@@ -1703,7 +1703,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:28:53</t>
+    <t>2026-08-27 03:35:29</t>
   </si>
   <si>
     <t>PERF_LOD_178</t>
@@ -1712,7 +1712,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:03</t>
+    <t>2026-08-27 03:35:39</t>
   </si>
   <si>
     <t>PERF_LOD_179</t>
@@ -1721,7 +1721,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:13</t>
+    <t>2026-08-27 03:35:49</t>
   </si>
   <si>
     <t>PERF_LOD_180</t>
@@ -1730,7 +1730,7 @@
     <t>Verify correct behavior of CPU Thermal Profile - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:23</t>
+    <t>2026-08-27 03:35:59</t>
   </si>
   <si>
     <t>PERF_LOD_181</t>
@@ -1742,7 +1742,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:33</t>
+    <t>2026-08-27 03:36:09</t>
   </si>
   <si>
     <t>PERF_LOD_182</t>
@@ -1751,7 +1751,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:43</t>
+    <t>2026-08-27 03:36:19</t>
   </si>
   <si>
     <t>PERF_LOD_183</t>
@@ -1760,7 +1760,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:29:53</t>
+    <t>2026-08-27 03:36:29</t>
   </si>
   <si>
     <t>PERF_LOD_184</t>
@@ -1769,7 +1769,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:03</t>
+    <t>2026-08-27 03:36:39</t>
   </si>
   <si>
     <t>PERF_LOD_185</t>
@@ -1778,7 +1778,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:13</t>
+    <t>2026-08-27 03:36:49</t>
   </si>
   <si>
     <t>PERF_LOD_186</t>
@@ -1787,7 +1787,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:23</t>
+    <t>2026-08-27 03:36:59</t>
   </si>
   <si>
     <t>PERF_LOD_187</t>
@@ -1796,7 +1796,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:33</t>
+    <t>2026-08-27 03:37:09</t>
   </si>
   <si>
     <t>PERF_LOD_188</t>
@@ -1805,7 +1805,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:43</t>
+    <t>2026-08-27 03:37:19</t>
   </si>
   <si>
     <t>PERF_LOD_189</t>
@@ -1814,7 +1814,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:30:53</t>
+    <t>2026-08-27 03:37:29</t>
   </si>
   <si>
     <t>PERF_LOD_190</t>
@@ -1823,7 +1823,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:03</t>
+    <t>2026-08-27 03:37:39</t>
   </si>
   <si>
     <t>PERF_LOD_191</t>
@@ -1832,7 +1832,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:13</t>
+    <t>2026-08-27 03:37:49</t>
   </si>
   <si>
     <t>PERF_LOD_192</t>
@@ -1841,7 +1841,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:23</t>
+    <t>2026-08-27 03:37:59</t>
   </si>
   <si>
     <t>PERF_LOD_193</t>
@@ -1850,7 +1850,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:33</t>
+    <t>2026-08-27 03:38:09</t>
   </si>
   <si>
     <t>PERF_LOD_194</t>
@@ -1859,7 +1859,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:43</t>
+    <t>2026-08-27 03:38:19</t>
   </si>
   <si>
     <t>PERF_LOD_195</t>
@@ -1868,7 +1868,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:31:53</t>
+    <t>2026-08-27 03:38:29</t>
   </si>
   <si>
     <t>PERF_LOD_196</t>
@@ -1877,7 +1877,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:03</t>
+    <t>2026-08-27 03:38:39</t>
   </si>
   <si>
     <t>PERF_LOD_197</t>
@@ -1886,7 +1886,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:13</t>
+    <t>2026-08-27 03:38:49</t>
   </si>
   <si>
     <t>PERF_LOD_198</t>
@@ -1895,7 +1895,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:23</t>
+    <t>2026-08-27 03:38:59</t>
   </si>
   <si>
     <t>PERF_LOD_199</t>
@@ -1904,7 +1904,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:33</t>
+    <t>2026-08-27 03:39:09</t>
   </si>
   <si>
     <t>PERF_LOD_200</t>
@@ -1913,7 +1913,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:43</t>
+    <t>2026-08-27 03:39:19</t>
   </si>
   <si>
     <t>PERF_LOD_201</t>
@@ -1922,7 +1922,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:32:53</t>
+    <t>2026-08-27 03:39:29</t>
   </si>
   <si>
     <t>PERF_LOD_202</t>
@@ -1931,7 +1931,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:03</t>
+    <t>2026-08-27 03:39:39</t>
   </si>
   <si>
     <t>PERF_LOD_203</t>
@@ -1940,7 +1940,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:13</t>
+    <t>2026-08-27 03:39:49</t>
   </si>
   <si>
     <t>PERF_LOD_204</t>
@@ -1949,7 +1949,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:23</t>
+    <t>2026-08-27 03:39:59</t>
   </si>
   <si>
     <t>PERF_LOD_205</t>
@@ -1958,7 +1958,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:33</t>
+    <t>2026-08-27 03:40:09</t>
   </si>
   <si>
     <t>PERF_LOD_206</t>
@@ -1967,7 +1967,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:43</t>
+    <t>2026-08-27 03:40:19</t>
   </si>
   <si>
     <t>PERF_LOD_207</t>
@@ -1976,7 +1976,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:33:53</t>
+    <t>2026-08-27 03:40:29</t>
   </si>
   <si>
     <t>PERF_LOD_208</t>
@@ -1985,7 +1985,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:03</t>
+    <t>2026-08-27 03:40:39</t>
   </si>
   <si>
     <t>PERF_LOD_209</t>
@@ -1994,7 +1994,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:13</t>
+    <t>2026-08-27 03:40:49</t>
   </si>
   <si>
     <t>PERF_LOD_210</t>
@@ -2003,7 +2003,7 @@
     <t>Verify correct behavior of RPS Scaling Limit - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:23</t>
+    <t>2026-08-27 03:40:59</t>
   </si>
   <si>
     <t>PERF_LOD_211</t>
@@ -2015,7 +2015,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:33</t>
+    <t>2026-08-27 03:41:09</t>
   </si>
   <si>
     <t>PERF_LOD_212</t>
@@ -2024,7 +2024,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:43</t>
+    <t>2026-08-27 03:41:19</t>
   </si>
   <si>
     <t>PERF_LOD_213</t>
@@ -2033,7 +2033,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:34:53</t>
+    <t>2026-08-27 03:41:29</t>
   </si>
   <si>
     <t>PERF_LOD_214</t>
@@ -2042,7 +2042,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:03</t>
+    <t>2026-08-27 03:41:39</t>
   </si>
   <si>
     <t>PERF_LOD_215</t>
@@ -2051,7 +2051,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:13</t>
+    <t>2026-08-27 03:41:49</t>
   </si>
   <si>
     <t>PERF_LOD_216</t>
@@ -2060,7 +2060,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:23</t>
+    <t>2026-08-27 03:41:59</t>
   </si>
   <si>
     <t>PERF_LOD_217</t>
@@ -2069,7 +2069,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:33</t>
+    <t>2026-08-27 03:42:09</t>
   </si>
   <si>
     <t>PERF_LOD_218</t>
@@ -2078,7 +2078,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:43</t>
+    <t>2026-08-27 03:42:19</t>
   </si>
   <si>
     <t>PERF_LOD_219</t>
@@ -2087,7 +2087,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:35:53</t>
+    <t>2026-08-27 03:42:29</t>
   </si>
   <si>
     <t>PERF_LOD_220</t>
@@ -2096,7 +2096,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:03</t>
+    <t>2026-08-27 03:42:39</t>
   </si>
   <si>
     <t>PERF_LOD_221</t>
@@ -2105,7 +2105,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:13</t>
+    <t>2026-08-27 03:42:49</t>
   </si>
   <si>
     <t>PERF_LOD_222</t>
@@ -2114,7 +2114,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:23</t>
+    <t>2026-08-27 03:42:59</t>
   </si>
   <si>
     <t>PERF_LOD_223</t>
@@ -2123,7 +2123,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:33</t>
+    <t>2026-08-27 03:43:09</t>
   </si>
   <si>
     <t>PERF_LOD_224</t>
@@ -2132,7 +2132,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:43</t>
+    <t>2026-08-27 03:43:19</t>
   </si>
   <si>
     <t>PERF_LOD_225</t>
@@ -2141,7 +2141,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:36:53</t>
+    <t>2026-08-27 03:43:29</t>
   </si>
   <si>
     <t>PERF_LOD_226</t>
@@ -2150,7 +2150,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:03</t>
+    <t>2026-08-27 03:43:39</t>
   </si>
   <si>
     <t>PERF_LOD_227</t>
@@ -2159,7 +2159,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:13</t>
+    <t>2026-08-27 03:43:49</t>
   </si>
   <si>
     <t>PERF_LOD_228</t>
@@ -2168,7 +2168,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:23</t>
+    <t>2026-08-27 03:43:59</t>
   </si>
   <si>
     <t>PERF_LOD_229</t>
@@ -2177,7 +2177,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:33</t>
+    <t>2026-08-27 03:44:09</t>
   </si>
   <si>
     <t>PERF_LOD_230</t>
@@ -2186,7 +2186,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:43</t>
+    <t>2026-08-27 03:44:19</t>
   </si>
   <si>
     <t>PERF_LOD_231</t>
@@ -2195,7 +2195,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:37:53</t>
+    <t>2026-08-27 03:44:29</t>
   </si>
   <si>
     <t>PERF_LOD_232</t>
@@ -2204,7 +2204,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:03</t>
+    <t>2026-08-27 03:44:39</t>
   </si>
   <si>
     <t>PERF_LOD_233</t>
@@ -2213,7 +2213,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:13</t>
+    <t>2026-08-27 03:44:49</t>
   </si>
   <si>
     <t>PERF_LOD_234</t>
@@ -2222,7 +2222,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:23</t>
+    <t>2026-08-27 03:44:59</t>
   </si>
   <si>
     <t>PERF_LOD_235</t>
@@ -2231,7 +2231,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:33</t>
+    <t>2026-08-27 03:45:09</t>
   </si>
   <si>
     <t>PERF_LOD_236</t>
@@ -2240,7 +2240,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:43</t>
+    <t>2026-08-27 03:45:19</t>
   </si>
   <si>
     <t>PERF_LOD_237</t>
@@ -2249,7 +2249,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:38:53</t>
+    <t>2026-08-27 03:45:29</t>
   </si>
   <si>
     <t>PERF_LOD_238</t>
@@ -2258,7 +2258,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:03</t>
+    <t>2026-08-27 03:45:39</t>
   </si>
   <si>
     <t>PERF_LOD_239</t>
@@ -2267,7 +2267,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:13</t>
+    <t>2026-08-27 03:45:49</t>
   </si>
   <si>
     <t>PERF_LOD_240</t>
@@ -2276,7 +2276,7 @@
     <t>Verify correct behavior of Network Backpressure - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:23</t>
+    <t>2026-08-27 03:45:59</t>
   </si>
   <si>
     <t>PERF_LOD_241</t>
@@ -2288,7 +2288,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:33</t>
+    <t>2026-08-27 03:46:09</t>
   </si>
   <si>
     <t>PERF_LOD_242</t>
@@ -2297,7 +2297,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:43</t>
+    <t>2026-08-27 03:46:19</t>
   </si>
   <si>
     <t>PERF_LOD_243</t>
@@ -2306,7 +2306,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:39:53</t>
+    <t>2026-08-27 03:46:29</t>
   </si>
   <si>
     <t>PERF_LOD_244</t>
@@ -2315,7 +2315,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:03</t>
+    <t>2026-08-27 03:46:39</t>
   </si>
   <si>
     <t>PERF_LOD_245</t>
@@ -2324,7 +2324,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:13</t>
+    <t>2026-08-27 03:46:49</t>
   </si>
   <si>
     <t>PERF_LOD_246</t>
@@ -2333,7 +2333,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:23</t>
+    <t>2026-08-27 03:46:59</t>
   </si>
   <si>
     <t>PERF_LOD_247</t>
@@ -2342,7 +2342,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:33</t>
+    <t>2026-08-27 03:47:09</t>
   </si>
   <si>
     <t>PERF_LOD_248</t>
@@ -2351,7 +2351,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:43</t>
+    <t>2026-08-27 03:47:19</t>
   </si>
   <si>
     <t>PERF_LOD_249</t>
@@ -2360,7 +2360,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:40:53</t>
+    <t>2026-08-27 03:47:29</t>
   </si>
   <si>
     <t>PERF_LOD_250</t>
@@ -2369,7 +2369,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:03</t>
+    <t>2026-08-27 03:47:39</t>
   </si>
   <si>
     <t>PERF_LOD_251</t>
@@ -2378,7 +2378,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:13</t>
+    <t>2026-08-27 03:47:49</t>
   </si>
   <si>
     <t>PERF_LOD_252</t>
@@ -2387,7 +2387,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:23</t>
+    <t>2026-08-27 03:47:59</t>
   </si>
   <si>
     <t>PERF_LOD_253</t>
@@ -2396,7 +2396,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:33</t>
+    <t>2026-08-27 03:48:09</t>
   </si>
   <si>
     <t>PERF_LOD_254</t>
@@ -2405,7 +2405,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:43</t>
+    <t>2026-08-27 03:48:19</t>
   </si>
   <si>
     <t>PERF_LOD_255</t>
@@ -2414,7 +2414,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:41:53</t>
+    <t>2026-08-27 03:48:29</t>
   </si>
   <si>
     <t>PERF_LOD_256</t>
@@ -2423,7 +2423,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:03</t>
+    <t>2026-08-27 03:48:39</t>
   </si>
   <si>
     <t>PERF_LOD_257</t>
@@ -2432,7 +2432,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:13</t>
+    <t>2026-08-27 03:48:49</t>
   </si>
   <si>
     <t>PERF_LOD_258</t>
@@ -2441,7 +2441,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:23</t>
+    <t>2026-08-27 03:48:59</t>
   </si>
   <si>
     <t>PERF_LOD_259</t>
@@ -2450,7 +2450,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:33</t>
+    <t>2026-08-27 03:49:09</t>
   </si>
   <si>
     <t>PERF_LOD_260</t>
@@ -2459,7 +2459,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:43</t>
+    <t>2026-08-27 03:49:19</t>
   </si>
   <si>
     <t>PERF_LOD_261</t>
@@ -2468,7 +2468,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:42:53</t>
+    <t>2026-08-27 03:49:29</t>
   </si>
   <si>
     <t>PERF_LOD_262</t>
@@ -2477,7 +2477,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:03</t>
+    <t>2026-08-27 03:49:39</t>
   </si>
   <si>
     <t>PERF_LOD_263</t>
@@ -2486,7 +2486,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:13</t>
+    <t>2026-08-27 03:49:49</t>
   </si>
   <si>
     <t>PERF_LOD_264</t>
@@ -2495,7 +2495,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:23</t>
+    <t>2026-08-27 03:49:59</t>
   </si>
   <si>
     <t>PERF_LOD_265</t>
@@ -2504,7 +2504,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:33</t>
+    <t>2026-08-27 03:50:09</t>
   </si>
   <si>
     <t>PERF_LOD_266</t>
@@ -2513,7 +2513,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:43</t>
+    <t>2026-08-27 03:50:19</t>
   </si>
   <si>
     <t>PERF_LOD_267</t>
@@ -2522,7 +2522,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:43:53</t>
+    <t>2026-08-27 03:50:29</t>
   </si>
   <si>
     <t>PERF_LOD_268</t>
@@ -2531,7 +2531,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:03</t>
+    <t>2026-08-27 03:50:39</t>
   </si>
   <si>
     <t>PERF_LOD_269</t>
@@ -2540,7 +2540,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:13</t>
+    <t>2026-08-27 03:50:49</t>
   </si>
   <si>
     <t>PERF_LOD_270</t>
@@ -2549,7 +2549,7 @@
     <t>Verify correct behavior of Disk I/O Latency - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:23</t>
+    <t>2026-08-27 03:50:59</t>
   </si>
   <si>
     <t>PERF_LOD_271</t>
@@ -2561,7 +2561,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #1</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:33</t>
+    <t>2026-08-27 03:51:09</t>
   </si>
   <si>
     <t>PERF_LOD_272</t>
@@ -2570,7 +2570,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #2</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:43</t>
+    <t>2026-08-27 03:51:19</t>
   </si>
   <si>
     <t>PERF_LOD_273</t>
@@ -2579,7 +2579,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #3</t>
   </si>
   <si>
-    <t>2026-08-27 03:44:53</t>
+    <t>2026-08-27 03:51:29</t>
   </si>
   <si>
     <t>PERF_LOD_274</t>
@@ -2588,7 +2588,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #4</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:03</t>
+    <t>2026-08-27 03:51:39</t>
   </si>
   <si>
     <t>PERF_LOD_275</t>
@@ -2597,7 +2597,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #5</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:13</t>
+    <t>2026-08-27 03:51:49</t>
   </si>
   <si>
     <t>PERF_LOD_276</t>
@@ -2606,7 +2606,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #6</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:23</t>
+    <t>2026-08-27 03:51:59</t>
   </si>
   <si>
     <t>PERF_LOD_277</t>
@@ -2615,7 +2615,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #7</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:33</t>
+    <t>2026-08-27 03:52:09</t>
   </si>
   <si>
     <t>PERF_LOD_278</t>
@@ -2624,7 +2624,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #8</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:43</t>
+    <t>2026-08-27 03:52:19</t>
   </si>
   <si>
     <t>PERF_LOD_279</t>
@@ -2633,7 +2633,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #9</t>
   </si>
   <si>
-    <t>2026-08-27 03:45:53</t>
+    <t>2026-08-27 03:52:29</t>
   </si>
   <si>
     <t>PERF_LOD_280</t>
@@ -2642,7 +2642,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #10</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:03</t>
+    <t>2026-08-27 03:52:39</t>
   </si>
   <si>
     <t>PERF_LOD_281</t>
@@ -2651,7 +2651,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #11</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:13</t>
+    <t>2026-08-27 03:52:49</t>
   </si>
   <si>
     <t>PERF_LOD_282</t>
@@ -2660,7 +2660,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #12</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:23</t>
+    <t>2026-08-27 03:52:59</t>
   </si>
   <si>
     <t>PERF_LOD_283</t>
@@ -2669,7 +2669,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #13</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:33</t>
+    <t>2026-08-27 03:53:09</t>
   </si>
   <si>
     <t>PERF_LOD_284</t>
@@ -2678,7 +2678,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #14</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:43</t>
+    <t>2026-08-27 03:53:19</t>
   </si>
   <si>
     <t>PERF_LOD_285</t>
@@ -2687,7 +2687,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #15</t>
   </si>
   <si>
-    <t>2026-08-27 03:46:53</t>
+    <t>2026-08-27 03:53:29</t>
   </si>
   <si>
     <t>PERF_LOD_286</t>
@@ -2696,7 +2696,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #16</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:03</t>
+    <t>2026-08-27 03:53:39</t>
   </si>
   <si>
     <t>PERF_LOD_287</t>
@@ -2705,7 +2705,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #17</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:13</t>
+    <t>2026-08-27 03:53:49</t>
   </si>
   <si>
     <t>PERF_LOD_288</t>
@@ -2714,7 +2714,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #18</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:23</t>
+    <t>2026-08-27 03:53:59</t>
   </si>
   <si>
     <t>PERF_LOD_289</t>
@@ -2723,7 +2723,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #19</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:33</t>
+    <t>2026-08-27 03:54:09</t>
   </si>
   <si>
     <t>PERF_LOD_290</t>
@@ -2732,7 +2732,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #20</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:43</t>
+    <t>2026-08-27 03:54:19</t>
   </si>
   <si>
     <t>PERF_LOD_291</t>
@@ -2741,7 +2741,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #21</t>
   </si>
   <si>
-    <t>2026-08-27 03:47:53</t>
+    <t>2026-08-27 03:54:29</t>
   </si>
   <si>
     <t>PERF_LOD_292</t>
@@ -2750,7 +2750,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #22</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:03</t>
+    <t>2026-08-27 03:54:39</t>
   </si>
   <si>
     <t>PERF_LOD_293</t>
@@ -2759,7 +2759,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #23</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:13</t>
+    <t>2026-08-27 03:54:49</t>
   </si>
   <si>
     <t>PERF_LOD_294</t>
@@ -2768,7 +2768,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #24</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:23</t>
+    <t>2026-08-27 03:54:59</t>
   </si>
   <si>
     <t>PERF_LOD_295</t>
@@ -2777,7 +2777,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #25</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:33</t>
+    <t>2026-08-27 03:55:09</t>
   </si>
   <si>
     <t>PERF_LOD_296</t>
@@ -2786,7 +2786,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #26</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:43</t>
+    <t>2026-08-27 03:55:19</t>
   </si>
   <si>
     <t>PERF_LOD_297</t>
@@ -2795,7 +2795,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #27</t>
   </si>
   <si>
-    <t>2026-08-27 03:48:53</t>
+    <t>2026-08-27 03:55:29</t>
   </si>
   <si>
     <t>PERF_LOD_298</t>
@@ -2804,7 +2804,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #28</t>
   </si>
   <si>
-    <t>2026-08-27 03:49:03</t>
+    <t>2026-08-27 03:55:39</t>
   </si>
   <si>
     <t>PERF_LOD_299</t>
@@ -2813,7 +2813,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #29</t>
   </si>
   <si>
-    <t>2026-08-27 03:49:13</t>
+    <t>2026-08-27 03:55:49</t>
   </si>
   <si>
     <t>PERF_LOD_300</t>
@@ -2822,7 +2822,7 @@
     <t>Verify correct behavior of Thread Allocator - test case variation #30</t>
   </si>
   <si>
-    <t>2026-08-27 03:49:23</t>
+    <t>2026-08-27 03:55:59</t>
   </si>
 </sst>
 </file>
@@ -3375,7 +3375,7 @@
         <v>29</v>
       </c>
       <c r="E2" s="3">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>30</v>
@@ -3395,7 +3395,7 @@
         <v>29</v>
       </c>
       <c r="E3">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="F3" t="s">
         <v>33</v>
@@ -3415,7 +3415,7 @@
         <v>29</v>
       </c>
       <c r="E4" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F4" s="3" t="s">
         <v>36</v>
@@ -3435,7 +3435,7 @@
         <v>29</v>
       </c>
       <c r="E5">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="F5" t="s">
         <v>39</v>
@@ -3455,7 +3455,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="3">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>42</v>
@@ -3475,7 +3475,7 @@
         <v>29</v>
       </c>
       <c r="E7">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
         <v>45</v>
@@ -3495,7 +3495,7 @@
         <v>29</v>
       </c>
       <c r="E8" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>48</v>
@@ -3515,7 +3515,7 @@
         <v>29</v>
       </c>
       <c r="E9">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
         <v>51</v>
@@ -3535,7 +3535,7 @@
         <v>29</v>
       </c>
       <c r="E10" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>54</v>
@@ -3555,7 +3555,7 @@
         <v>29</v>
       </c>
       <c r="E11">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F11" t="s">
         <v>57</v>
@@ -3575,7 +3575,7 @@
         <v>29</v>
       </c>
       <c r="E12" s="3">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F12" s="3" t="s">
         <v>60</v>
@@ -3595,7 +3595,7 @@
         <v>29</v>
       </c>
       <c r="E13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F13" t="s">
         <v>63</v>
@@ -3615,7 +3615,7 @@
         <v>29</v>
       </c>
       <c r="E14" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>66</v>
@@ -3635,7 +3635,7 @@
         <v>29</v>
       </c>
       <c r="E15">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F15" t="s">
         <v>69</v>
@@ -3655,7 +3655,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="3">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>72</v>
@@ -3675,7 +3675,7 @@
         <v>29</v>
       </c>
       <c r="E17">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F17" t="s">
         <v>75</v>
@@ -3695,7 +3695,7 @@
         <v>29</v>
       </c>
       <c r="E18" s="3">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>78</v>
@@ -3715,7 +3715,7 @@
         <v>29</v>
       </c>
       <c r="E19">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F19" t="s">
         <v>81</v>
@@ -3735,7 +3735,7 @@
         <v>29</v>
       </c>
       <c r="E20" s="3">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>84</v>
@@ -3755,7 +3755,7 @@
         <v>29</v>
       </c>
       <c r="E21">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F21" t="s">
         <v>87</v>
@@ -3775,7 +3775,7 @@
         <v>29</v>
       </c>
       <c r="E22" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>90</v>
@@ -3795,7 +3795,7 @@
         <v>29</v>
       </c>
       <c r="E23">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F23" t="s">
         <v>93</v>
@@ -3815,7 +3815,7 @@
         <v>29</v>
       </c>
       <c r="E24" s="3">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>96</v>
@@ -3835,7 +3835,7 @@
         <v>29</v>
       </c>
       <c r="E25">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="F25" t="s">
         <v>99</v>
@@ -3855,7 +3855,7 @@
         <v>29</v>
       </c>
       <c r="E26" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>102</v>
@@ -3875,7 +3875,7 @@
         <v>29</v>
       </c>
       <c r="E27">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F27" t="s">
         <v>105</v>
@@ -3895,7 +3895,7 @@
         <v>29</v>
       </c>
       <c r="E28" s="3">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>108</v>
@@ -3915,7 +3915,7 @@
         <v>29</v>
       </c>
       <c r="E29">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F29" t="s">
         <v>111</v>
@@ -3935,7 +3935,7 @@
         <v>29</v>
       </c>
       <c r="E30" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>114</v>
@@ -3955,7 +3955,7 @@
         <v>29</v>
       </c>
       <c r="E31">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F31" t="s">
         <v>117</v>
@@ -3975,7 +3975,7 @@
         <v>29</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>121</v>
@@ -3995,7 +3995,7 @@
         <v>29</v>
       </c>
       <c r="E33">
-        <v>23</v>
+        <v>6</v>
       </c>
       <c r="F33" t="s">
         <v>124</v>
@@ -4015,7 +4015,7 @@
         <v>29</v>
       </c>
       <c r="E34" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>127</v>
@@ -4035,7 +4035,7 @@
         <v>29</v>
       </c>
       <c r="E35">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="F35" t="s">
         <v>130</v>
@@ -4055,7 +4055,7 @@
         <v>29</v>
       </c>
       <c r="E36" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>133</v>
@@ -4075,7 +4075,7 @@
         <v>29</v>
       </c>
       <c r="E37">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F37" t="s">
         <v>136</v>
@@ -4095,7 +4095,7 @@
         <v>29</v>
       </c>
       <c r="E38" s="3">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>139</v>
@@ -4115,7 +4115,7 @@
         <v>29</v>
       </c>
       <c r="E39">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F39" t="s">
         <v>142</v>
@@ -4135,7 +4135,7 @@
         <v>29</v>
       </c>
       <c r="E40" s="3">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>145</v>
@@ -4175,7 +4175,7 @@
         <v>29</v>
       </c>
       <c r="E42" s="3">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>151</v>
@@ -4195,7 +4195,7 @@
         <v>29</v>
       </c>
       <c r="E43">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="F43" t="s">
         <v>154</v>
@@ -4215,7 +4215,7 @@
         <v>29</v>
       </c>
       <c r="E44" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>157</v>
@@ -4235,7 +4235,7 @@
         <v>29</v>
       </c>
       <c r="E45">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F45" t="s">
         <v>160</v>
@@ -4275,7 +4275,7 @@
         <v>29</v>
       </c>
       <c r="E47">
-        <v>22</v>
+        <v>9</v>
       </c>
       <c r="F47" t="s">
         <v>166</v>
@@ -4295,7 +4295,7 @@
         <v>29</v>
       </c>
       <c r="E48" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>169</v>
@@ -4315,7 +4315,7 @@
         <v>29</v>
       </c>
       <c r="E49">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="F49" t="s">
         <v>172</v>
@@ -4335,7 +4335,7 @@
         <v>29</v>
       </c>
       <c r="E50" s="3">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>175</v>
@@ -4355,7 +4355,7 @@
         <v>29</v>
       </c>
       <c r="E51">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F51" t="s">
         <v>178</v>
@@ -4375,7 +4375,7 @@
         <v>29</v>
       </c>
       <c r="E52" s="3">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>181</v>
@@ -4395,7 +4395,7 @@
         <v>29</v>
       </c>
       <c r="E53">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F53" t="s">
         <v>184</v>
@@ -4415,7 +4415,7 @@
         <v>29</v>
       </c>
       <c r="E54" s="3">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>187</v>
@@ -4435,7 +4435,7 @@
         <v>29</v>
       </c>
       <c r="E55">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F55" t="s">
         <v>190</v>
@@ -4455,7 +4455,7 @@
         <v>29</v>
       </c>
       <c r="E56" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>193</v>
@@ -4475,7 +4475,7 @@
         <v>29</v>
       </c>
       <c r="E57">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F57" t="s">
         <v>196</v>
@@ -4495,7 +4495,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="3">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>199</v>
@@ -4515,7 +4515,7 @@
         <v>29</v>
       </c>
       <c r="E59">
-        <v>5</v>
+        <v>21</v>
       </c>
       <c r="F59" t="s">
         <v>202</v>
@@ -4535,7 +4535,7 @@
         <v>29</v>
       </c>
       <c r="E60" s="3">
-        <v>19</v>
+        <v>7</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>205</v>
@@ -4555,7 +4555,7 @@
         <v>29</v>
       </c>
       <c r="E61">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F61" t="s">
         <v>208</v>
@@ -4575,7 +4575,7 @@
         <v>29</v>
       </c>
       <c r="E62" s="3">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>212</v>
@@ -4595,7 +4595,7 @@
         <v>29</v>
       </c>
       <c r="E63">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F63" t="s">
         <v>215</v>
@@ -4615,7 +4615,7 @@
         <v>29</v>
       </c>
       <c r="E64" s="3">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>218</v>
@@ -4635,7 +4635,7 @@
         <v>29</v>
       </c>
       <c r="E65">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="F65" t="s">
         <v>221</v>
@@ -4655,7 +4655,7 @@
         <v>29</v>
       </c>
       <c r="E66" s="3">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>224</v>
@@ -4675,7 +4675,7 @@
         <v>29</v>
       </c>
       <c r="E67">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="F67" t="s">
         <v>227</v>
@@ -4695,7 +4695,7 @@
         <v>29</v>
       </c>
       <c r="E68" s="3">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>230</v>
@@ -4735,7 +4735,7 @@
         <v>29</v>
       </c>
       <c r="E70" s="3">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>236</v>
@@ -4775,7 +4775,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>242</v>
@@ -4795,7 +4795,7 @@
         <v>29</v>
       </c>
       <c r="E73">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F73" t="s">
         <v>245</v>
@@ -4815,7 +4815,7 @@
         <v>29</v>
       </c>
       <c r="E74" s="3">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>248</v>
@@ -4835,7 +4835,7 @@
         <v>29</v>
       </c>
       <c r="E75">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F75" t="s">
         <v>251</v>
@@ -4855,7 +4855,7 @@
         <v>29</v>
       </c>
       <c r="E76" s="3">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="F76" s="3" t="s">
         <v>254</v>
@@ -4875,7 +4875,7 @@
         <v>29</v>
       </c>
       <c r="E77">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="F77" t="s">
         <v>257</v>
@@ -4895,7 +4895,7 @@
         <v>29</v>
       </c>
       <c r="E78" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F78" s="3" t="s">
         <v>260</v>
@@ -4915,7 +4915,7 @@
         <v>29</v>
       </c>
       <c r="E79">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="F79" t="s">
         <v>263</v>
@@ -4955,7 +4955,7 @@
         <v>29</v>
       </c>
       <c r="E81">
-        <v>24</v>
+        <v>9</v>
       </c>
       <c r="F81" t="s">
         <v>269</v>
@@ -4975,7 +4975,7 @@
         <v>29</v>
       </c>
       <c r="E82" s="3">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>272</v>
@@ -4995,7 +4995,7 @@
         <v>29</v>
       </c>
       <c r="E83">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F83" t="s">
         <v>275</v>
@@ -5015,7 +5015,7 @@
         <v>29</v>
       </c>
       <c r="E84" s="3">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>278</v>
@@ -5035,7 +5035,7 @@
         <v>29</v>
       </c>
       <c r="E85">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F85" t="s">
         <v>281</v>
@@ -5055,7 +5055,7 @@
         <v>29</v>
       </c>
       <c r="E86" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F86" s="3" t="s">
         <v>284</v>
@@ -5075,7 +5075,7 @@
         <v>29</v>
       </c>
       <c r="E87">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F87" t="s">
         <v>287</v>
@@ -5095,7 +5095,7 @@
         <v>29</v>
       </c>
       <c r="E88" s="3">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="F88" s="3" t="s">
         <v>290</v>
@@ -5115,7 +5115,7 @@
         <v>29</v>
       </c>
       <c r="E89">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F89" t="s">
         <v>293</v>
@@ -5135,7 +5135,7 @@
         <v>29</v>
       </c>
       <c r="E90" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="F90" s="3" t="s">
         <v>296</v>
@@ -5155,7 +5155,7 @@
         <v>29</v>
       </c>
       <c r="E91">
-        <v>7</v>
+        <v>23</v>
       </c>
       <c r="F91" t="s">
         <v>299</v>
@@ -5175,7 +5175,7 @@
         <v>29</v>
       </c>
       <c r="E92" s="3">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F92" s="3" t="s">
         <v>303</v>
@@ -5195,7 +5195,7 @@
         <v>29</v>
       </c>
       <c r="E93">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="F93" t="s">
         <v>306</v>
@@ -5215,7 +5215,7 @@
         <v>29</v>
       </c>
       <c r="E94" s="3">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="F94" s="3" t="s">
         <v>309</v>
@@ -5235,7 +5235,7 @@
         <v>29</v>
       </c>
       <c r="E95">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F95" t="s">
         <v>312</v>
@@ -5255,7 +5255,7 @@
         <v>29</v>
       </c>
       <c r="E96" s="3">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F96" s="3" t="s">
         <v>315</v>
@@ -5275,7 +5275,7 @@
         <v>29</v>
       </c>
       <c r="E97">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F97" t="s">
         <v>318</v>
@@ -5295,7 +5295,7 @@
         <v>29</v>
       </c>
       <c r="E98" s="3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="F98" s="3" t="s">
         <v>321</v>
@@ -5315,7 +5315,7 @@
         <v>29</v>
       </c>
       <c r="E99">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="F99" t="s">
         <v>324</v>
@@ -5335,7 +5335,7 @@
         <v>29</v>
       </c>
       <c r="E100" s="3">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="F100" s="3" t="s">
         <v>327</v>
@@ -5355,7 +5355,7 @@
         <v>29</v>
       </c>
       <c r="E101">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F101" t="s">
         <v>330</v>
@@ -5375,7 +5375,7 @@
         <v>29</v>
       </c>
       <c r="E102" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F102" s="3" t="s">
         <v>333</v>
@@ -5395,7 +5395,7 @@
         <v>29</v>
       </c>
       <c r="E103">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="F103" t="s">
         <v>336</v>
@@ -5415,7 +5415,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F104" s="3" t="s">
         <v>339</v>
@@ -5435,7 +5435,7 @@
         <v>29</v>
       </c>
       <c r="E105">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="F105" t="s">
         <v>342</v>
@@ -5455,7 +5455,7 @@
         <v>29</v>
       </c>
       <c r="E106" s="3">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="F106" s="3" t="s">
         <v>345</v>
@@ -5475,7 +5475,7 @@
         <v>29</v>
       </c>
       <c r="E107">
-        <v>22</v>
+        <v>7</v>
       </c>
       <c r="F107" t="s">
         <v>348</v>
@@ -5495,7 +5495,7 @@
         <v>29</v>
       </c>
       <c r="E108" s="3">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="F108" s="3" t="s">
         <v>351</v>
@@ -5515,7 +5515,7 @@
         <v>29</v>
       </c>
       <c r="E109">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F109" t="s">
         <v>354</v>
@@ -5535,7 +5535,7 @@
         <v>29</v>
       </c>
       <c r="E110" s="3">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="F110" s="3" t="s">
         <v>357</v>
@@ -5555,7 +5555,7 @@
         <v>29</v>
       </c>
       <c r="E111">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F111" t="s">
         <v>360</v>
@@ -5575,7 +5575,7 @@
         <v>29</v>
       </c>
       <c r="E112" s="3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F112" s="3" t="s">
         <v>363</v>
@@ -5595,7 +5595,7 @@
         <v>29</v>
       </c>
       <c r="E113">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F113" t="s">
         <v>366</v>
@@ -5635,7 +5635,7 @@
         <v>29</v>
       </c>
       <c r="E115">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="F115" t="s">
         <v>372</v>
@@ -5655,7 +5655,7 @@
         <v>29</v>
       </c>
       <c r="E116" s="3">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="F116" s="3" t="s">
         <v>375</v>
@@ -5675,7 +5675,7 @@
         <v>29</v>
       </c>
       <c r="E117">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="F117" t="s">
         <v>378</v>
@@ -5695,7 +5695,7 @@
         <v>29</v>
       </c>
       <c r="E118" s="3">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="F118" s="3" t="s">
         <v>381</v>
@@ -5755,7 +5755,7 @@
         <v>29</v>
       </c>
       <c r="E121">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F121" t="s">
         <v>390</v>
@@ -5775,7 +5775,7 @@
         <v>29</v>
       </c>
       <c r="E122" s="3">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="F122" s="3" t="s">
         <v>394</v>
@@ -5795,7 +5795,7 @@
         <v>29</v>
       </c>
       <c r="E123">
-        <v>8</v>
+        <v>21</v>
       </c>
       <c r="F123" t="s">
         <v>397</v>
@@ -5835,7 +5835,7 @@
         <v>29</v>
       </c>
       <c r="E125">
-        <v>14</v>
+        <v>24</v>
       </c>
       <c r="F125" t="s">
         <v>403</v>
@@ -5855,7 +5855,7 @@
         <v>29</v>
       </c>
       <c r="E126" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="F126" s="3" t="s">
         <v>406</v>
@@ -5875,7 +5875,7 @@
         <v>29</v>
       </c>
       <c r="E127">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F127" t="s">
         <v>409</v>
@@ -5915,7 +5915,7 @@
         <v>29</v>
       </c>
       <c r="E129">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="F129" t="s">
         <v>415</v>
@@ -5935,7 +5935,7 @@
         <v>29</v>
       </c>
       <c r="E130" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F130" s="3" t="s">
         <v>418</v>
@@ -5955,7 +5955,7 @@
         <v>29</v>
       </c>
       <c r="E131">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F131" t="s">
         <v>421</v>
@@ -5975,7 +5975,7 @@
         <v>29</v>
       </c>
       <c r="E132" s="3">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F132" s="3" t="s">
         <v>424</v>
@@ -5995,7 +5995,7 @@
         <v>29</v>
       </c>
       <c r="E133">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F133" t="s">
         <v>427</v>
@@ -6015,7 +6015,7 @@
         <v>29</v>
       </c>
       <c r="E134" s="3">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F134" s="3" t="s">
         <v>430</v>
@@ -6035,7 +6035,7 @@
         <v>29</v>
       </c>
       <c r="E135">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F135" t="s">
         <v>433</v>
@@ -6055,7 +6055,7 @@
         <v>29</v>
       </c>
       <c r="E136" s="3">
-        <v>7</v>
+        <v>24</v>
       </c>
       <c r="F136" s="3" t="s">
         <v>436</v>
@@ -6075,7 +6075,7 @@
         <v>29</v>
       </c>
       <c r="E137">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="F137" t="s">
         <v>439</v>
@@ -6095,7 +6095,7 @@
         <v>29</v>
       </c>
       <c r="E138" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F138" s="3" t="s">
         <v>442</v>
@@ -6115,7 +6115,7 @@
         <v>29</v>
       </c>
       <c r="E139">
-        <v>22</v>
+        <v>5</v>
       </c>
       <c r="F139" t="s">
         <v>445</v>
@@ -6135,7 +6135,7 @@
         <v>29</v>
       </c>
       <c r="E140" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F140" s="3" t="s">
         <v>448</v>
@@ -6155,7 +6155,7 @@
         <v>29</v>
       </c>
       <c r="E141">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F141" t="s">
         <v>451</v>
@@ -6175,7 +6175,7 @@
         <v>29</v>
       </c>
       <c r="E142" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F142" s="3" t="s">
         <v>454</v>
@@ -6195,7 +6195,7 @@
         <v>29</v>
       </c>
       <c r="E143">
-        <v>19</v>
+        <v>9</v>
       </c>
       <c r="F143" t="s">
         <v>457</v>
@@ -6215,7 +6215,7 @@
         <v>29</v>
       </c>
       <c r="E144" s="3">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F144" s="3" t="s">
         <v>460</v>
@@ -6235,7 +6235,7 @@
         <v>29</v>
       </c>
       <c r="E145">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="F145" t="s">
         <v>463</v>
@@ -6255,7 +6255,7 @@
         <v>29</v>
       </c>
       <c r="E146" s="3">
-        <v>14</v>
+        <v>23</v>
       </c>
       <c r="F146" s="3" t="s">
         <v>466</v>
@@ -6275,7 +6275,7 @@
         <v>29</v>
       </c>
       <c r="E147">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F147" t="s">
         <v>469</v>
@@ -6295,7 +6295,7 @@
         <v>29</v>
       </c>
       <c r="E148" s="3">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="F148" s="3" t="s">
         <v>472</v>
@@ -6315,7 +6315,7 @@
         <v>29</v>
       </c>
       <c r="E149">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="F149" t="s">
         <v>475</v>
@@ -6335,7 +6335,7 @@
         <v>29</v>
       </c>
       <c r="E150" s="3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F150" s="3" t="s">
         <v>478</v>
@@ -6355,7 +6355,7 @@
         <v>29</v>
       </c>
       <c r="E151">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F151" t="s">
         <v>481</v>
@@ -6375,7 +6375,7 @@
         <v>29</v>
       </c>
       <c r="E152" s="3">
-        <v>7</v>
+        <v>22</v>
       </c>
       <c r="F152" s="3" t="s">
         <v>485</v>
@@ -6395,7 +6395,7 @@
         <v>29</v>
       </c>
       <c r="E153">
-        <v>6</v>
+        <v>23</v>
       </c>
       <c r="F153" t="s">
         <v>488</v>
@@ -6415,7 +6415,7 @@
         <v>29</v>
       </c>
       <c r="E154" s="3">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="F154" s="3" t="s">
         <v>491</v>
@@ -6435,7 +6435,7 @@
         <v>29</v>
       </c>
       <c r="E155">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F155" t="s">
         <v>494</v>
@@ -6455,7 +6455,7 @@
         <v>29</v>
       </c>
       <c r="E156" s="3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F156" s="3" t="s">
         <v>497</v>
@@ -6475,7 +6475,7 @@
         <v>29</v>
       </c>
       <c r="E157">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="F157" t="s">
         <v>500</v>
@@ -6515,7 +6515,7 @@
         <v>29</v>
       </c>
       <c r="E159">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F159" t="s">
         <v>506</v>
@@ -6535,7 +6535,7 @@
         <v>29</v>
       </c>
       <c r="E160" s="3">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F160" s="3" t="s">
         <v>509</v>
@@ -6555,7 +6555,7 @@
         <v>29</v>
       </c>
       <c r="E161">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F161" t="s">
         <v>512</v>
@@ -6575,7 +6575,7 @@
         <v>29</v>
       </c>
       <c r="E162" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F162" s="3" t="s">
         <v>515</v>
@@ -6595,7 +6595,7 @@
         <v>29</v>
       </c>
       <c r="E163">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F163" t="s">
         <v>518</v>
@@ -6635,7 +6635,7 @@
         <v>29</v>
       </c>
       <c r="E165">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F165" t="s">
         <v>524</v>
@@ -6655,7 +6655,7 @@
         <v>29</v>
       </c>
       <c r="E166" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F166" s="3" t="s">
         <v>527</v>
@@ -6675,7 +6675,7 @@
         <v>29</v>
       </c>
       <c r="E167">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F167" t="s">
         <v>530</v>
@@ -6695,7 +6695,7 @@
         <v>29</v>
       </c>
       <c r="E168" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F168" s="3" t="s">
         <v>533</v>
@@ -6715,7 +6715,7 @@
         <v>29</v>
       </c>
       <c r="E169">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="F169" t="s">
         <v>536</v>
@@ -6735,7 +6735,7 @@
         <v>29</v>
       </c>
       <c r="E170" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F170" s="3" t="s">
         <v>539</v>
@@ -6755,7 +6755,7 @@
         <v>29</v>
       </c>
       <c r="E171">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F171" t="s">
         <v>542</v>
@@ -6775,7 +6775,7 @@
         <v>29</v>
       </c>
       <c r="E172" s="3">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F172" s="3" t="s">
         <v>545</v>
@@ -6795,7 +6795,7 @@
         <v>29</v>
       </c>
       <c r="E173">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="F173" t="s">
         <v>548</v>
@@ -6815,7 +6815,7 @@
         <v>29</v>
       </c>
       <c r="E174" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F174" s="3" t="s">
         <v>551</v>
@@ -6835,7 +6835,7 @@
         <v>29</v>
       </c>
       <c r="E175">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F175" t="s">
         <v>554</v>
@@ -6855,7 +6855,7 @@
         <v>29</v>
       </c>
       <c r="E176" s="3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F176" s="3" t="s">
         <v>557</v>
@@ -6875,7 +6875,7 @@
         <v>29</v>
       </c>
       <c r="E177">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="F177" t="s">
         <v>560</v>
@@ -6895,7 +6895,7 @@
         <v>29</v>
       </c>
       <c r="E178" s="3">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F178" s="3" t="s">
         <v>563</v>
@@ -6915,7 +6915,7 @@
         <v>29</v>
       </c>
       <c r="E179">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="F179" t="s">
         <v>566</v>
@@ -6935,7 +6935,7 @@
         <v>29</v>
       </c>
       <c r="E180" s="3">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F180" s="3" t="s">
         <v>569</v>
@@ -6955,7 +6955,7 @@
         <v>29</v>
       </c>
       <c r="E181">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F181" t="s">
         <v>572</v>
@@ -6995,7 +6995,7 @@
         <v>29</v>
       </c>
       <c r="E183">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F183" t="s">
         <v>579</v>
@@ -7015,7 +7015,7 @@
         <v>29</v>
       </c>
       <c r="E184" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F184" s="3" t="s">
         <v>582</v>
@@ -7035,7 +7035,7 @@
         <v>29</v>
       </c>
       <c r="E185">
-        <v>18</v>
+        <v>5</v>
       </c>
       <c r="F185" t="s">
         <v>585</v>
@@ -7055,7 +7055,7 @@
         <v>29</v>
       </c>
       <c r="E186" s="3">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="F186" s="3" t="s">
         <v>588</v>
@@ -7075,7 +7075,7 @@
         <v>29</v>
       </c>
       <c r="E187">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F187" t="s">
         <v>591</v>
@@ -7095,7 +7095,7 @@
         <v>29</v>
       </c>
       <c r="E188" s="3">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="F188" s="3" t="s">
         <v>594</v>
@@ -7115,7 +7115,7 @@
         <v>29</v>
       </c>
       <c r="E189">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F189" t="s">
         <v>597</v>
@@ -7155,7 +7155,7 @@
         <v>29</v>
       </c>
       <c r="E191">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F191" t="s">
         <v>603</v>
@@ -7175,7 +7175,7 @@
         <v>29</v>
       </c>
       <c r="E192" s="3">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="F192" s="3" t="s">
         <v>606</v>
@@ -7195,7 +7195,7 @@
         <v>29</v>
       </c>
       <c r="E193">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F193" t="s">
         <v>609</v>
@@ -7215,7 +7215,7 @@
         <v>29</v>
       </c>
       <c r="E194" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F194" s="3" t="s">
         <v>612</v>
@@ -7235,7 +7235,7 @@
         <v>29</v>
       </c>
       <c r="E195">
-        <v>15</v>
+        <v>21</v>
       </c>
       <c r="F195" t="s">
         <v>615</v>
@@ -7255,7 +7255,7 @@
         <v>29</v>
       </c>
       <c r="E196" s="3">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F196" s="3" t="s">
         <v>618</v>
@@ -7275,7 +7275,7 @@
         <v>29</v>
       </c>
       <c r="E197">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F197" t="s">
         <v>621</v>
@@ -7295,7 +7295,7 @@
         <v>29</v>
       </c>
       <c r="E198" s="3">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F198" s="3" t="s">
         <v>624</v>
@@ -7315,7 +7315,7 @@
         <v>29</v>
       </c>
       <c r="E199">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F199" t="s">
         <v>627</v>
@@ -7355,7 +7355,7 @@
         <v>29</v>
       </c>
       <c r="E201">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F201" t="s">
         <v>633</v>
@@ -7375,7 +7375,7 @@
         <v>29</v>
       </c>
       <c r="E202" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F202" s="3" t="s">
         <v>636</v>
@@ -7395,7 +7395,7 @@
         <v>29</v>
       </c>
       <c r="E203">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F203" t="s">
         <v>639</v>
@@ -7415,7 +7415,7 @@
         <v>29</v>
       </c>
       <c r="E204" s="3">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="F204" s="3" t="s">
         <v>642</v>
@@ -7435,7 +7435,7 @@
         <v>29</v>
       </c>
       <c r="E205">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="F205" t="s">
         <v>645</v>
@@ -7455,7 +7455,7 @@
         <v>29</v>
       </c>
       <c r="E206" s="3">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="F206" s="3" t="s">
         <v>648</v>
@@ -7475,7 +7475,7 @@
         <v>29</v>
       </c>
       <c r="E207">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F207" t="s">
         <v>651</v>
@@ -7495,7 +7495,7 @@
         <v>29</v>
       </c>
       <c r="E208" s="3">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="F208" s="3" t="s">
         <v>654</v>
@@ -7515,7 +7515,7 @@
         <v>29</v>
       </c>
       <c r="E209">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F209" t="s">
         <v>657</v>
@@ -7535,7 +7535,7 @@
         <v>29</v>
       </c>
       <c r="E210" s="3">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F210" s="3" t="s">
         <v>660</v>
@@ -7555,7 +7555,7 @@
         <v>29</v>
       </c>
       <c r="E211">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F211" t="s">
         <v>663</v>
@@ -7575,7 +7575,7 @@
         <v>29</v>
       </c>
       <c r="E212" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F212" s="3" t="s">
         <v>667</v>
@@ -7595,7 +7595,7 @@
         <v>29</v>
       </c>
       <c r="E213">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="F213" t="s">
         <v>670</v>
@@ -7615,7 +7615,7 @@
         <v>29</v>
       </c>
       <c r="E214" s="3">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="F214" s="3" t="s">
         <v>673</v>
@@ -7635,7 +7635,7 @@
         <v>29</v>
       </c>
       <c r="E215">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="F215" t="s">
         <v>676</v>
@@ -7655,7 +7655,7 @@
         <v>29</v>
       </c>
       <c r="E216" s="3">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="F216" s="3" t="s">
         <v>679</v>
@@ -7675,7 +7675,7 @@
         <v>29</v>
       </c>
       <c r="E217">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F217" t="s">
         <v>682</v>
@@ -7695,7 +7695,7 @@
         <v>29</v>
       </c>
       <c r="E218" s="3">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F218" s="3" t="s">
         <v>685</v>
@@ -7715,7 +7715,7 @@
         <v>29</v>
       </c>
       <c r="E219">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F219" t="s">
         <v>688</v>
@@ -7735,7 +7735,7 @@
         <v>29</v>
       </c>
       <c r="E220" s="3">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="F220" s="3" t="s">
         <v>691</v>
@@ -7795,7 +7795,7 @@
         <v>29</v>
       </c>
       <c r="E223">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F223" t="s">
         <v>700</v>
@@ -7815,7 +7815,7 @@
         <v>29</v>
       </c>
       <c r="E224" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F224" s="3" t="s">
         <v>703</v>
@@ -7835,7 +7835,7 @@
         <v>29</v>
       </c>
       <c r="E225">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="F225" t="s">
         <v>706</v>
@@ -7855,7 +7855,7 @@
         <v>29</v>
       </c>
       <c r="E226" s="3">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F226" s="3" t="s">
         <v>709</v>
@@ -7875,7 +7875,7 @@
         <v>29</v>
       </c>
       <c r="E227">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F227" t="s">
         <v>712</v>
@@ -7895,7 +7895,7 @@
         <v>29</v>
       </c>
       <c r="E228" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F228" s="3" t="s">
         <v>715</v>
@@ -7915,7 +7915,7 @@
         <v>29</v>
       </c>
       <c r="E229">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="F229" t="s">
         <v>718</v>
@@ -7955,7 +7955,7 @@
         <v>29</v>
       </c>
       <c r="E231">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="F231" t="s">
         <v>724</v>
@@ -7975,7 +7975,7 @@
         <v>29</v>
       </c>
       <c r="E232" s="3">
-        <v>19</v>
+        <v>5</v>
       </c>
       <c r="F232" s="3" t="s">
         <v>727</v>
@@ -7995,7 +7995,7 @@
         <v>29</v>
       </c>
       <c r="E233">
-        <v>6</v>
+        <v>21</v>
       </c>
       <c r="F233" t="s">
         <v>730</v>
@@ -8015,7 +8015,7 @@
         <v>29</v>
       </c>
       <c r="E234" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="F234" s="3" t="s">
         <v>733</v>
@@ -8035,7 +8035,7 @@
         <v>29</v>
       </c>
       <c r="E235">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F235" t="s">
         <v>736</v>
@@ -8055,7 +8055,7 @@
         <v>29</v>
       </c>
       <c r="E236" s="3">
-        <v>9</v>
+        <v>23</v>
       </c>
       <c r="F236" s="3" t="s">
         <v>739</v>
@@ -8075,7 +8075,7 @@
         <v>29</v>
       </c>
       <c r="E237">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="F237" t="s">
         <v>742</v>
@@ -8095,7 +8095,7 @@
         <v>29</v>
       </c>
       <c r="E238" s="3">
-        <v>5</v>
+        <v>23</v>
       </c>
       <c r="F238" s="3" t="s">
         <v>745</v>
@@ -8115,7 +8115,7 @@
         <v>29</v>
       </c>
       <c r="E239">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="F239" t="s">
         <v>748</v>
@@ -8135,7 +8135,7 @@
         <v>29</v>
       </c>
       <c r="E240" s="3">
-        <v>22</v>
+        <v>13</v>
       </c>
       <c r="F240" s="3" t="s">
         <v>751</v>
@@ -8155,7 +8155,7 @@
         <v>29</v>
       </c>
       <c r="E241">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F241" t="s">
         <v>754</v>
@@ -8175,7 +8175,7 @@
         <v>29</v>
       </c>
       <c r="E242" s="3">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="F242" s="3" t="s">
         <v>758</v>
@@ -8195,7 +8195,7 @@
         <v>29</v>
       </c>
       <c r="E243">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F243" t="s">
         <v>761</v>
@@ -8215,7 +8215,7 @@
         <v>29</v>
       </c>
       <c r="E244" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F244" s="3" t="s">
         <v>764</v>
@@ -8235,7 +8235,7 @@
         <v>29</v>
       </c>
       <c r="E245">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="F245" t="s">
         <v>767</v>
@@ -8255,7 +8255,7 @@
         <v>29</v>
       </c>
       <c r="E246" s="3">
-        <v>21</v>
+        <v>9</v>
       </c>
       <c r="F246" s="3" t="s">
         <v>770</v>
@@ -8275,7 +8275,7 @@
         <v>29</v>
       </c>
       <c r="E247">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="F247" t="s">
         <v>773</v>
@@ -8295,7 +8295,7 @@
         <v>29</v>
       </c>
       <c r="E248" s="3">
-        <v>11</v>
+        <v>24</v>
       </c>
       <c r="F248" s="3" t="s">
         <v>776</v>
@@ -8315,7 +8315,7 @@
         <v>29</v>
       </c>
       <c r="E249">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="F249" t="s">
         <v>779</v>
@@ -8335,7 +8335,7 @@
         <v>29</v>
       </c>
       <c r="E250" s="3">
-        <v>17</v>
+        <v>24</v>
       </c>
       <c r="F250" s="3" t="s">
         <v>782</v>
@@ -8355,7 +8355,7 @@
         <v>29</v>
       </c>
       <c r="E251">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F251" t="s">
         <v>785</v>
@@ -8375,7 +8375,7 @@
         <v>29</v>
       </c>
       <c r="E252" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F252" s="3" t="s">
         <v>788</v>
@@ -8395,7 +8395,7 @@
         <v>29</v>
       </c>
       <c r="E253">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="F253" t="s">
         <v>791</v>
@@ -8415,7 +8415,7 @@
         <v>29</v>
       </c>
       <c r="E254" s="3">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F254" s="3" t="s">
         <v>794</v>
@@ -8435,7 +8435,7 @@
         <v>29</v>
       </c>
       <c r="E255">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F255" t="s">
         <v>797</v>
@@ -8455,7 +8455,7 @@
         <v>29</v>
       </c>
       <c r="E256" s="3">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="F256" s="3" t="s">
         <v>800</v>
@@ -8475,7 +8475,7 @@
         <v>29</v>
       </c>
       <c r="E257">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F257" t="s">
         <v>803</v>
@@ -8495,7 +8495,7 @@
         <v>29</v>
       </c>
       <c r="E258" s="3">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F258" s="3" t="s">
         <v>806</v>
@@ -8515,7 +8515,7 @@
         <v>29</v>
       </c>
       <c r="E259">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="F259" t="s">
         <v>809</v>
@@ -8535,7 +8535,7 @@
         <v>29</v>
       </c>
       <c r="E260" s="3">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F260" s="3" t="s">
         <v>812</v>
@@ -8575,7 +8575,7 @@
         <v>29</v>
       </c>
       <c r="E262" s="3">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F262" s="3" t="s">
         <v>818</v>
@@ -8595,7 +8595,7 @@
         <v>29</v>
       </c>
       <c r="E263">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F263" t="s">
         <v>821</v>
@@ -8615,7 +8615,7 @@
         <v>29</v>
       </c>
       <c r="E264" s="3">
-        <v>9</v>
+        <v>24</v>
       </c>
       <c r="F264" s="3" t="s">
         <v>824</v>
@@ -8635,7 +8635,7 @@
         <v>29</v>
       </c>
       <c r="E265">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="F265" t="s">
         <v>827</v>
@@ -8675,7 +8675,7 @@
         <v>29</v>
       </c>
       <c r="E267">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="F267" t="s">
         <v>833</v>
@@ -8695,7 +8695,7 @@
         <v>29</v>
       </c>
       <c r="E268" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="F268" s="3" t="s">
         <v>836</v>
@@ -8715,7 +8715,7 @@
         <v>29</v>
       </c>
       <c r="E269">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F269" t="s">
         <v>839</v>
@@ -8735,7 +8735,7 @@
         <v>29</v>
       </c>
       <c r="E270" s="3">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="F270" s="3" t="s">
         <v>842</v>
@@ -8755,7 +8755,7 @@
         <v>29</v>
       </c>
       <c r="E271">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="F271" t="s">
         <v>845</v>
@@ -8775,7 +8775,7 @@
         <v>29</v>
       </c>
       <c r="E272" s="3">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="F272" s="3" t="s">
         <v>849</v>
@@ -8795,7 +8795,7 @@
         <v>29</v>
       </c>
       <c r="E273">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F273" t="s">
         <v>852</v>
@@ -8815,7 +8815,7 @@
         <v>29</v>
       </c>
       <c r="E274" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F274" s="3" t="s">
         <v>855</v>
@@ -8835,7 +8835,7 @@
         <v>29</v>
       </c>
       <c r="E275">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F275" t="s">
         <v>858</v>
@@ -8855,7 +8855,7 @@
         <v>29</v>
       </c>
       <c r="E276" s="3">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F276" s="3" t="s">
         <v>861</v>
@@ -8875,7 +8875,7 @@
         <v>29</v>
       </c>
       <c r="E277">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="F277" t="s">
         <v>864</v>
@@ -8895,7 +8895,7 @@
         <v>29</v>
       </c>
       <c r="E278" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F278" s="3" t="s">
         <v>867</v>
@@ -8915,7 +8915,7 @@
         <v>29</v>
       </c>
       <c r="E279">
-        <v>24</v>
+        <v>6</v>
       </c>
       <c r="F279" t="s">
         <v>870</v>
@@ -8935,7 +8935,7 @@
         <v>29</v>
       </c>
       <c r="E280" s="3">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="F280" s="3" t="s">
         <v>873</v>
@@ -8955,7 +8955,7 @@
         <v>29</v>
       </c>
       <c r="E281">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="F281" t="s">
         <v>876</v>
@@ -8975,7 +8975,7 @@
         <v>29</v>
       </c>
       <c r="E282" s="3">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F282" s="3" t="s">
         <v>879</v>
@@ -9015,7 +9015,7 @@
         <v>29</v>
       </c>
       <c r="E284" s="3">
-        <v>6</v>
+        <v>20</v>
       </c>
       <c r="F284" s="3" t="s">
         <v>885</v>
@@ -9035,7 +9035,7 @@
         <v>29</v>
       </c>
       <c r="E285">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="F285" t="s">
         <v>888</v>
@@ -9055,7 +9055,7 @@
         <v>29</v>
       </c>
       <c r="E286" s="3">
-        <v>19</v>
+        <v>6</v>
       </c>
       <c r="F286" s="3" t="s">
         <v>891</v>
@@ -9075,7 +9075,7 @@
         <v>29</v>
       </c>
       <c r="E287">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="F287" t="s">
         <v>894</v>
@@ -9095,7 +9095,7 @@
         <v>29</v>
       </c>
       <c r="E288" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F288" s="3" t="s">
         <v>897</v>
@@ -9115,7 +9115,7 @@
         <v>29</v>
       </c>
       <c r="E289">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="F289" t="s">
         <v>900</v>
@@ -9135,7 +9135,7 @@
         <v>29</v>
       </c>
       <c r="E290" s="3">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="F290" s="3" t="s">
         <v>903</v>
@@ -9155,7 +9155,7 @@
         <v>29</v>
       </c>
       <c r="E291">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="F291" t="s">
         <v>906</v>
@@ -9175,7 +9175,7 @@
         <v>29</v>
       </c>
       <c r="E292" s="3">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="F292" s="3" t="s">
         <v>909</v>
@@ -9195,7 +9195,7 @@
         <v>29</v>
       </c>
       <c r="E293">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="F293" t="s">
         <v>912</v>
@@ -9215,7 +9215,7 @@
         <v>29</v>
       </c>
       <c r="E294" s="3">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="F294" s="3" t="s">
         <v>915</v>
@@ -9235,7 +9235,7 @@
         <v>29</v>
       </c>
       <c r="E295">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F295" t="s">
         <v>918</v>
@@ -9275,7 +9275,7 @@
         <v>29</v>
       </c>
       <c r="E297">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="F297" t="s">
         <v>924</v>
@@ -9295,7 +9295,7 @@
         <v>29</v>
       </c>
       <c r="E298" s="3">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="F298" s="3" t="s">
         <v>927</v>
@@ -9315,7 +9315,7 @@
         <v>29</v>
       </c>
       <c r="E299">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F299" t="s">
         <v>930</v>
@@ -9355,7 +9355,7 @@
         <v>29</v>
       </c>
       <c r="E301">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="F301" t="s">
         <v>936</v>
